--- a/public/exports/29189706.xlsx
+++ b/public/exports/29189706.xlsx
@@ -181,16 +181,16 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t xml:space="preserve">2647308</t>
+          <t xml:space="preserve">5447821</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t xml:space="preserve">14</t>
+          <t xml:space="preserve">12</t>
         </is>
       </c>
       <c r="F4">
-        <v>922</v>
+        <v>345</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -231,16 +231,16 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t xml:space="preserve">5447821</t>
+          <t xml:space="preserve">726971, 5446776</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t xml:space="preserve">12</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F5">
-        <v>345</v>
+        <v>318</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -281,7 +281,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t xml:space="preserve">726971, 5446776</t>
+          <t xml:space="preserve">726974, 5446779</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -290,7 +290,7 @@
         </is>
       </c>
       <c r="F6">
-        <v>318</v>
+        <v>1658</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -331,16 +331,16 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t xml:space="preserve">726974, 5446779</t>
+          <t xml:space="preserve">727288, 9467816</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">22</t>
         </is>
       </c>
       <c r="F7">
-        <v>1658</v>
+        <v>680</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -381,16 +381,16 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t xml:space="preserve">727288, 9467816</t>
+          <t xml:space="preserve">727536, 7992424</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t xml:space="preserve">22</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F8">
-        <v>680</v>
+        <v>600</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -431,16 +431,16 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t xml:space="preserve">727536, 7992424</t>
+          <t xml:space="preserve">727707, 5445271</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">29</t>
         </is>
       </c>
       <c r="F9">
-        <v>600</v>
+        <v>1384</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -481,16 +481,16 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t xml:space="preserve">727703, 9281555</t>
+          <t xml:space="preserve">727715, 5446764</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F10">
-        <v>374</v>
+        <v>356</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -531,16 +531,16 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t xml:space="preserve">727707, 5445271</t>
+          <t xml:space="preserve">727717, 5445867</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t xml:space="preserve">29</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F11">
-        <v>1384</v>
+        <v>456</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -581,16 +581,16 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t xml:space="preserve">727708, 9281555</t>
+          <t xml:space="preserve">7885723, 100938670</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t xml:space="preserve">15</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="F12">
-        <v>705</v>
+        <v>384</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -631,16 +631,16 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t xml:space="preserve">727715, 5446764</t>
+          <t xml:space="preserve">9467816</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">145</t>
         </is>
       </c>
       <c r="F13">
-        <v>356</v>
+        <v>3083</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -681,16 +681,16 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t xml:space="preserve">727717, 5445867</t>
+          <t xml:space="preserve">9467816</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
       <c r="F14">
-        <v>456</v>
+        <v>1095</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -731,30 +731,30 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t xml:space="preserve">727740, 9281555</t>
+          <t xml:space="preserve">2647308</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t xml:space="preserve">13</t>
+          <t xml:space="preserve">14</t>
         </is>
       </c>
       <c r="F15">
-        <v>2179</v>
+        <v>922</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">200015627</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2019-06-23</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mangler energimærke</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -781,30 +781,30 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t xml:space="preserve">727744, 7137947</t>
+          <t xml:space="preserve">5445177</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F16">
-        <v>752</v>
+        <v>301</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">200016330</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2019-06-29</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mangler energimærke</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -831,30 +831,30 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t xml:space="preserve">7885723, 100938670</t>
+          <t xml:space="preserve">727708, 9281555</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">15</t>
         </is>
       </c>
       <c r="F17">
-        <v>384</v>
+        <v>705</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">310035433</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2023-04-17</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mangler energimærke</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -881,30 +881,30 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t xml:space="preserve">9467816</t>
+          <t xml:space="preserve">727740, 9281555</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t xml:space="preserve">145</t>
+          <t xml:space="preserve">13</t>
         </is>
       </c>
       <c r="F18">
-        <v>3083</v>
+        <v>2179</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">311063628</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2024-07-07</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mangler energimærke</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -931,35 +931,35 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t xml:space="preserve">9467816</t>
+          <t xml:space="preserve">2647308</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F19">
-        <v>1095</v>
+        <v>1815</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">311289781</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2027-12-20</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mangler energimærke</t>
+          <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ja</t>
+          <t xml:space="preserve">Nej</t>
         </is>
       </c>
     </row>
@@ -981,7 +981,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t xml:space="preserve">5445177</t>
+          <t xml:space="preserve">100059307</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -990,26 +990,26 @@
         </is>
       </c>
       <c r="F20">
-        <v>301</v>
+        <v>2301</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t xml:space="preserve">200016330</t>
+          <t xml:space="preserve">311483550</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-06-29</t>
+          <t xml:space="preserve">2030-12-17</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t xml:space="preserve">Udløbet</t>
+          <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ja</t>
+          <t xml:space="preserve">Nej</t>
         </is>
       </c>
     </row>
@@ -1031,7 +1031,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t xml:space="preserve">5445530</t>
+          <t xml:space="preserve">2642837</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -1040,26 +1040,26 @@
         </is>
       </c>
       <c r="F21">
-        <v>2330</v>
+        <v>662</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t xml:space="preserve">200016411</t>
+          <t xml:space="preserve">311495046</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-06-30</t>
+          <t xml:space="preserve">2031-02-12</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t xml:space="preserve">Udløbet</t>
+          <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ja</t>
+          <t xml:space="preserve">Nej</t>
         </is>
       </c>
     </row>
@@ -1081,25 +1081,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t xml:space="preserve">2647308</t>
+          <t xml:space="preserve">2642837</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="F22">
-        <v>1815</v>
+        <v>2794</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t xml:space="preserve">311289781</t>
+          <t xml:space="preserve">311495046</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-12-20</t>
+          <t xml:space="preserve">2031-02-12</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -1131,25 +1131,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t xml:space="preserve">100059307</t>
+          <t xml:space="preserve">2642837</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
       <c r="F23">
-        <v>2301</v>
+        <v>314</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t xml:space="preserve">311483550</t>
+          <t xml:space="preserve">311495046</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-12-17</t>
+          <t xml:space="preserve">2031-02-12</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -1181,7 +1181,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t xml:space="preserve">2642837</t>
+          <t xml:space="preserve">5447028</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -1190,16 +1190,16 @@
         </is>
       </c>
       <c r="F24">
-        <v>662</v>
+        <v>543</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t xml:space="preserve">311495046</t>
+          <t xml:space="preserve">311497381</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-02-12</t>
+          <t xml:space="preserve">2031-02-22</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -1231,25 +1231,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t xml:space="preserve">2642837</t>
+          <t xml:space="preserve">8573246</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F25">
-        <v>2794</v>
+        <v>5771</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t xml:space="preserve">311495046</t>
+          <t xml:space="preserve">311497472</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-02-12</t>
+          <t xml:space="preserve">2031-02-22</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -1281,25 +1281,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t xml:space="preserve">2642837</t>
+          <t xml:space="preserve">727744, 7137947</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="F26">
-        <v>314</v>
+        <v>752</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t xml:space="preserve">311495046</t>
+          <t xml:space="preserve">311498092</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-02-12</t>
+          <t xml:space="preserve">2031-02-24</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -1331,7 +1331,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t xml:space="preserve">5447028</t>
+          <t xml:space="preserve">100044506</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -1340,16 +1340,16 @@
         </is>
       </c>
       <c r="F27">
-        <v>543</v>
+        <v>285</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t xml:space="preserve">311497381</t>
+          <t xml:space="preserve">311505577</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-02-22</t>
+          <t xml:space="preserve">2031-03-22</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -1381,7 +1381,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t xml:space="preserve">8573246</t>
+          <t xml:space="preserve">1329020</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -1390,16 +1390,16 @@
         </is>
       </c>
       <c r="F28">
-        <v>5771</v>
+        <v>2329</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t xml:space="preserve">311497472</t>
+          <t xml:space="preserve">311505625</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-02-22</t>
+          <t xml:space="preserve">2031-03-22</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t xml:space="preserve">100044506</t>
+          <t xml:space="preserve">2649327</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -1440,11 +1440,11 @@
         </is>
       </c>
       <c r="F29">
-        <v>285</v>
+        <v>919</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t xml:space="preserve">311505585</t>
+          <t xml:space="preserve">311505590</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -1481,7 +1481,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t xml:space="preserve">1329020</t>
+          <t xml:space="preserve">2657334</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -1490,11 +1490,11 @@
         </is>
       </c>
       <c r="F30">
-        <v>2329</v>
+        <v>1008</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t xml:space="preserve">311505625</t>
+          <t xml:space="preserve">311505605</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -1531,7 +1531,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t xml:space="preserve">2649327</t>
+          <t xml:space="preserve">5445095</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -1540,11 +1540,11 @@
         </is>
       </c>
       <c r="F31">
-        <v>919</v>
+        <v>2098</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t xml:space="preserve">311505590</t>
+          <t xml:space="preserve">311505621</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t xml:space="preserve">2657334</t>
+          <t xml:space="preserve">8045593</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -1590,11 +1590,11 @@
         </is>
       </c>
       <c r="F32">
-        <v>1008</v>
+        <v>582</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t xml:space="preserve">311505605</t>
+          <t xml:space="preserve">311505594</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -1631,25 +1631,25 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t xml:space="preserve">5445095</t>
+          <t xml:space="preserve">2642378</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F33">
-        <v>2098</v>
+        <v>344</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t xml:space="preserve">311505621</t>
+          <t xml:space="preserve">311518199</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-03-22</t>
+          <t xml:space="preserve">2031-05-06</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -1681,25 +1681,25 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t xml:space="preserve">8045593</t>
+          <t xml:space="preserve">2642378</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="F34">
-        <v>582</v>
+        <v>1019</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t xml:space="preserve">311505594</t>
+          <t xml:space="preserve">311518199</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-03-22</t>
+          <t xml:space="preserve">2031-05-06</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -1731,20 +1731,20 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t xml:space="preserve">2642378</t>
+          <t xml:space="preserve">2642402</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F35">
-        <v>344</v>
+        <v>260</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t xml:space="preserve">311518199</t>
+          <t xml:space="preserve">311598345</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -1781,20 +1781,20 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t xml:space="preserve">2642378</t>
+          <t xml:space="preserve">2658030</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="F36">
-        <v>1019</v>
+        <v>260</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t xml:space="preserve">311518199</t>
+          <t xml:space="preserve">311518262</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -1831,7 +1831,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t xml:space="preserve">2642402</t>
+          <t xml:space="preserve">5446101</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -1840,11 +1840,11 @@
         </is>
       </c>
       <c r="F37">
-        <v>260</v>
+        <v>1797</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t xml:space="preserve">311598345</t>
+          <t xml:space="preserve">311518286</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -1881,20 +1881,20 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t xml:space="preserve">2658030</t>
+          <t xml:space="preserve">5446234</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F38">
-        <v>260</v>
+        <v>1516</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t xml:space="preserve">311518262</t>
+          <t xml:space="preserve">311518290</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -1931,7 +1931,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t xml:space="preserve">5446101</t>
+          <t xml:space="preserve">5446917</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -1940,11 +1940,11 @@
         </is>
       </c>
       <c r="F39">
-        <v>1797</v>
+        <v>923</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t xml:space="preserve">311518286</t>
+          <t xml:space="preserve">311518236</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -1981,7 +1981,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t xml:space="preserve">5446234</t>
+          <t xml:space="preserve">2646524</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -1990,16 +1990,16 @@
         </is>
       </c>
       <c r="F40">
-        <v>1516</v>
+        <v>362</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t xml:space="preserve">311518290</t>
+          <t xml:space="preserve">311526236</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-05-06</t>
+          <t xml:space="preserve">2031-06-08</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -2031,7 +2031,7 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t xml:space="preserve">5446917</t>
+          <t xml:space="preserve">2657922</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -2040,16 +2040,16 @@
         </is>
       </c>
       <c r="F41">
-        <v>923</v>
+        <v>3580</v>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t xml:space="preserve">311518236</t>
+          <t xml:space="preserve">311526226</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-05-06</t>
+          <t xml:space="preserve">2031-06-08</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -2081,7 +2081,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t xml:space="preserve">2646524</t>
+          <t xml:space="preserve">7771570</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -2090,11 +2090,11 @@
         </is>
       </c>
       <c r="F42">
-        <v>362</v>
+        <v>4136</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t xml:space="preserve">311526236</t>
+          <t xml:space="preserve">311526259</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t xml:space="preserve">2657922</t>
+          <t xml:space="preserve">2646560</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -2140,16 +2140,16 @@
         </is>
       </c>
       <c r="F43">
-        <v>3580</v>
+        <v>7542</v>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t xml:space="preserve">311526226</t>
+          <t xml:space="preserve">311540126</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-06-08</t>
+          <t xml:space="preserve">2031-08-11</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -2181,25 +2181,25 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t xml:space="preserve">7771570</t>
+          <t xml:space="preserve">2646560</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F44">
-        <v>4136</v>
+        <v>1970</v>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t xml:space="preserve">311526259</t>
+          <t xml:space="preserve">311540105</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-06-08</t>
+          <t xml:space="preserve">2031-08-11</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -2236,15 +2236,15 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="F45">
-        <v>7542</v>
+        <v>526</v>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t xml:space="preserve">311540126</t>
+          <t xml:space="preserve">311540125</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -2281,25 +2281,25 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t xml:space="preserve">2646560</t>
+          <t xml:space="preserve">727703, 9281555</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
       <c r="F46">
-        <v>1970</v>
+        <v>374</v>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t xml:space="preserve">311540105</t>
+          <t xml:space="preserve">311545701</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-08-11</t>
+          <t xml:space="preserve">2031-09-03</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -2331,25 +2331,25 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t xml:space="preserve">2646560</t>
+          <t xml:space="preserve">2647942</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F47">
-        <v>526</v>
+        <v>3098</v>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t xml:space="preserve">311540125</t>
+          <t xml:space="preserve">311557515</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-08-11</t>
+          <t xml:space="preserve">2031-10-26</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -2381,25 +2381,25 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t xml:space="preserve">2644084</t>
+          <t xml:space="preserve">2647942</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">10</t>
         </is>
       </c>
       <c r="F48">
-        <v>3173</v>
+        <v>1047</v>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t xml:space="preserve">311546212</t>
+          <t xml:space="preserve">311557515</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-09-07</t>
+          <t xml:space="preserve">2031-10-26</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
@@ -2436,15 +2436,15 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F49">
-        <v>3098</v>
+        <v>1557</v>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t xml:space="preserve">311557521</t>
+          <t xml:space="preserve">311557515</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -2486,15 +2486,15 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t xml:space="preserve">10</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="F50">
-        <v>1047</v>
+        <v>935</v>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t xml:space="preserve">311557521</t>
+          <t xml:space="preserve">311557515</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -2531,25 +2531,25 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t xml:space="preserve">2647942</t>
+          <t xml:space="preserve">7137947</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="F51">
-        <v>1557</v>
+        <v>2407</v>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t xml:space="preserve">311557518</t>
+          <t xml:space="preserve">311586428</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-10-26</t>
+          <t xml:space="preserve">2032-03-18</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
@@ -2581,25 +2581,25 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t xml:space="preserve">2647942</t>
+          <t xml:space="preserve">5446281</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F52">
-        <v>935</v>
+        <v>957</v>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t xml:space="preserve">311557521</t>
+          <t xml:space="preserve">311587820</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-10-26</t>
+          <t xml:space="preserve">2032-03-24</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
@@ -2631,25 +2631,25 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t xml:space="preserve">7137947</t>
+          <t xml:space="preserve">2644386</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F53">
-        <v>2407</v>
+        <v>272</v>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t xml:space="preserve">311586428</t>
+          <t xml:space="preserve">311589703</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-03-18</t>
+          <t xml:space="preserve">2032-03-31</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
@@ -2681,25 +2681,25 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t xml:space="preserve">5446281</t>
+          <t xml:space="preserve">2644386</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="F54">
-        <v>957</v>
+        <v>334</v>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t xml:space="preserve">311587820</t>
+          <t xml:space="preserve">311589703</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-03-24</t>
+          <t xml:space="preserve">2032-03-31</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
@@ -2736,20 +2736,20 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F55">
-        <v>272</v>
+        <v>1673</v>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t xml:space="preserve">311589703</t>
+          <t xml:space="preserve">311590388</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-03-31</t>
+          <t xml:space="preserve">2032-04-04</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
@@ -2781,25 +2781,25 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t xml:space="preserve">2644386</t>
+          <t xml:space="preserve">5445199</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F56">
-        <v>334</v>
+        <v>426</v>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t xml:space="preserve">311589703</t>
+          <t xml:space="preserve">311590569</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-03-31</t>
+          <t xml:space="preserve">2032-04-04</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
@@ -2831,25 +2831,25 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t xml:space="preserve">2644386</t>
+          <t xml:space="preserve">7885723</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F57">
-        <v>1673</v>
+        <v>1510</v>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t xml:space="preserve">311590388</t>
+          <t xml:space="preserve">311592215</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-04-04</t>
+          <t xml:space="preserve">2032-04-10</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
@@ -2881,7 +2881,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t xml:space="preserve">5445199</t>
+          <t xml:space="preserve">2648084</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -2890,16 +2890,16 @@
         </is>
       </c>
       <c r="F58">
-        <v>426</v>
+        <v>1894</v>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t xml:space="preserve">311590569</t>
+          <t xml:space="preserve">311594782</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-04-04</t>
+          <t xml:space="preserve">2032-04-22</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t xml:space="preserve">7885723</t>
+          <t xml:space="preserve">7136071</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -2940,16 +2940,16 @@
         </is>
       </c>
       <c r="F59">
-        <v>1510</v>
+        <v>703</v>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t xml:space="preserve">311592215</t>
+          <t xml:space="preserve">311595067</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-04-10</t>
+          <t xml:space="preserve">2032-04-25</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
@@ -2981,7 +2981,7 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t xml:space="preserve">2648084</t>
+          <t xml:space="preserve">5445543</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -2990,16 +2990,16 @@
         </is>
       </c>
       <c r="F60">
-        <v>1894</v>
+        <v>338</v>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t xml:space="preserve">311594782</t>
+          <t xml:space="preserve">311596137</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-04-22</t>
+          <t xml:space="preserve">2032-04-28</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
@@ -3031,7 +3031,7 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t xml:space="preserve">7136071</t>
+          <t xml:space="preserve">5447721</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -3040,16 +3040,16 @@
         </is>
       </c>
       <c r="F61">
-        <v>703</v>
+        <v>658</v>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t xml:space="preserve">311595067</t>
+          <t xml:space="preserve">311597138</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-04-25</t>
+          <t xml:space="preserve">2032-05-02</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
@@ -3081,25 +3081,25 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t xml:space="preserve">5445530</t>
+          <t xml:space="preserve">5447821</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F62">
-        <v>1254</v>
+        <v>3067</v>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t xml:space="preserve">311595700</t>
+          <t xml:space="preserve">311597531</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-04-27</t>
+          <t xml:space="preserve">2032-05-03</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
@@ -3131,25 +3131,25 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t xml:space="preserve">5445530</t>
+          <t xml:space="preserve">100063809</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F63">
-        <v>1521</v>
+        <v>1109</v>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t xml:space="preserve">311595700</t>
+          <t xml:space="preserve">311598079</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-04-27</t>
+          <t xml:space="preserve">2032-05-05</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
@@ -3181,25 +3181,25 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t xml:space="preserve">5445530</t>
+          <t xml:space="preserve">2647942</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="F64">
-        <v>2032</v>
+        <v>603</v>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t xml:space="preserve">311595700</t>
+          <t xml:space="preserve">311598123</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-04-27</t>
+          <t xml:space="preserve">2032-05-05</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
@@ -3231,25 +3231,25 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t xml:space="preserve">5445530</t>
+          <t xml:space="preserve">5447821</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="F65">
-        <v>425</v>
+        <v>611</v>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t xml:space="preserve">311595700</t>
+          <t xml:space="preserve">311598741</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-04-27</t>
+          <t xml:space="preserve">2032-05-09</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
@@ -3281,25 +3281,25 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t xml:space="preserve">5445543</t>
+          <t xml:space="preserve">2647308</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F66">
-        <v>338</v>
+        <v>921</v>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t xml:space="preserve">311596137</t>
+          <t xml:space="preserve">311599005</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-04-28</t>
+          <t xml:space="preserve">2032-05-10</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
@@ -3331,25 +3331,25 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t xml:space="preserve">5447721</t>
+          <t xml:space="preserve">2647308</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F67">
-        <v>658</v>
+        <v>1104</v>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t xml:space="preserve">311597138</t>
+          <t xml:space="preserve">311599005</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-05-02</t>
+          <t xml:space="preserve">2032-05-10</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
@@ -3381,25 +3381,25 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t xml:space="preserve">5447821</t>
+          <t xml:space="preserve">2647308</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="F68">
-        <v>3067</v>
+        <v>679</v>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t xml:space="preserve">311597531</t>
+          <t xml:space="preserve">311599005</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-05-03</t>
+          <t xml:space="preserve">2032-05-10</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
@@ -3431,25 +3431,25 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t xml:space="preserve">100063809</t>
+          <t xml:space="preserve">2647308</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="F69">
-        <v>1109</v>
+        <v>487</v>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t xml:space="preserve">311598079</t>
+          <t xml:space="preserve">311599005</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-05-05</t>
+          <t xml:space="preserve">2032-05-10</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
@@ -3481,25 +3481,25 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t xml:space="preserve">2647942</t>
+          <t xml:space="preserve">9281555</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">51</t>
         </is>
       </c>
       <c r="F70">
-        <v>603</v>
+        <v>256</v>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t xml:space="preserve">311598123</t>
+          <t xml:space="preserve">311600397</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-05-05</t>
+          <t xml:space="preserve">2032-05-16</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
@@ -3531,25 +3531,25 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t xml:space="preserve">5447821</t>
+          <t xml:space="preserve">9281555</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">53</t>
         </is>
       </c>
       <c r="F71">
-        <v>611</v>
+        <v>360</v>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t xml:space="preserve">311598741</t>
+          <t xml:space="preserve">311600401</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-05-09</t>
+          <t xml:space="preserve">2032-05-16</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
@@ -3581,25 +3581,25 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t xml:space="preserve">2647308</t>
+          <t xml:space="preserve">2647035</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F72">
-        <v>921</v>
+        <v>2732</v>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t xml:space="preserve">311599005</t>
+          <t xml:space="preserve">311601059</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-05-10</t>
+          <t xml:space="preserve">2032-05-18</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
@@ -3631,25 +3631,25 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t xml:space="preserve">2647308</t>
+          <t xml:space="preserve">2647035</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F73">
-        <v>1104</v>
+        <v>1074</v>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t xml:space="preserve">311599005</t>
+          <t xml:space="preserve">311601058</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-05-10</t>
+          <t xml:space="preserve">2032-05-18</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
@@ -3681,25 +3681,25 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t xml:space="preserve">2647308</t>
+          <t xml:space="preserve">5445605</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F74">
-        <v>679</v>
+        <v>1869</v>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t xml:space="preserve">311599005</t>
+          <t xml:space="preserve">311601070</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-05-10</t>
+          <t xml:space="preserve">2032-05-18</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
@@ -3731,25 +3731,25 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t xml:space="preserve">2647308</t>
+          <t xml:space="preserve">5445605</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F75">
-        <v>487</v>
+        <v>738</v>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t xml:space="preserve">311599005</t>
+          <t xml:space="preserve">311601070</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-05-10</t>
+          <t xml:space="preserve">2032-05-18</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
@@ -3781,25 +3781,25 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t xml:space="preserve">9281555</t>
+          <t xml:space="preserve">2657345</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t xml:space="preserve">51</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F76">
-        <v>256</v>
+        <v>5119</v>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t xml:space="preserve">311600397</t>
+          <t xml:space="preserve">311602646</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-05-16</t>
+          <t xml:space="preserve">2032-05-24</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
@@ -3831,25 +3831,25 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t xml:space="preserve">9281555</t>
+          <t xml:space="preserve">7137947</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t xml:space="preserve">53</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F77">
-        <v>360</v>
+        <v>573</v>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t xml:space="preserve">311600401</t>
+          <t xml:space="preserve">311604349</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-05-16</t>
+          <t xml:space="preserve">2032-05-31</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
@@ -3881,25 +3881,25 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t xml:space="preserve">2647035</t>
+          <t xml:space="preserve">2645740</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F78">
-        <v>2732</v>
+        <v>324</v>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t xml:space="preserve">311601059</t>
+          <t xml:space="preserve">311616001</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-05-18</t>
+          <t xml:space="preserve">2032-07-18</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
@@ -3931,25 +3931,25 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t xml:space="preserve">2647035</t>
+          <t xml:space="preserve">2645740</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="F79">
-        <v>1074</v>
+        <v>350</v>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t xml:space="preserve">311601058</t>
+          <t xml:space="preserve">311616001</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-05-18</t>
+          <t xml:space="preserve">2032-07-18</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
@@ -3981,25 +3981,25 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t xml:space="preserve">5445605</t>
+          <t xml:space="preserve">2645740</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="F80">
-        <v>1869</v>
+        <v>742</v>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t xml:space="preserve">311601070</t>
+          <t xml:space="preserve">311616001</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-05-18</t>
+          <t xml:space="preserve">2032-07-18</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
@@ -4031,7 +4031,7 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t xml:space="preserve">5445605</t>
+          <t xml:space="preserve">7137947</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
@@ -4040,16 +4040,16 @@
         </is>
       </c>
       <c r="F81">
-        <v>738</v>
+        <v>7353</v>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t xml:space="preserve">311601070</t>
+          <t xml:space="preserve">311617388</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-05-18</t>
+          <t xml:space="preserve">2032-07-27</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
@@ -4081,25 +4081,25 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t xml:space="preserve">2657345</t>
+          <t xml:space="preserve">7137947</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F82">
-        <v>5119</v>
+        <v>3458</v>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t xml:space="preserve">311602646</t>
+          <t xml:space="preserve">311617330</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-05-24</t>
+          <t xml:space="preserve">2032-07-27</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
@@ -4131,7 +4131,7 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t xml:space="preserve">7137947</t>
+          <t xml:space="preserve">7089254</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
@@ -4140,16 +4140,16 @@
         </is>
       </c>
       <c r="F83">
-        <v>573</v>
+        <v>831</v>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t xml:space="preserve">311604349</t>
+          <t xml:space="preserve">311621564</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-05-31</t>
+          <t xml:space="preserve">2032-08-19</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
@@ -4181,25 +4181,25 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t xml:space="preserve">2645740</t>
+          <t xml:space="preserve">5445530</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F84">
-        <v>324</v>
+        <v>2330</v>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t xml:space="preserve">311614889</t>
+          <t xml:space="preserve">311676080</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-07-12</t>
+          <t xml:space="preserve">2033-04-25</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
@@ -4231,25 +4231,25 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t xml:space="preserve">2645740</t>
+          <t xml:space="preserve">5445530</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F85">
-        <v>350</v>
+        <v>1254</v>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t xml:space="preserve">311614889</t>
+          <t xml:space="preserve">311676080</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-07-12</t>
+          <t xml:space="preserve">2033-04-25</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
@@ -4281,25 +4281,25 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t xml:space="preserve">2645740</t>
+          <t xml:space="preserve">5445530</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F86">
-        <v>742</v>
+        <v>1521</v>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t xml:space="preserve">311614907</t>
+          <t xml:space="preserve">311676080</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-07-12</t>
+          <t xml:space="preserve">2033-04-25</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
@@ -4331,25 +4331,25 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t xml:space="preserve">7137947</t>
+          <t xml:space="preserve">5445530</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="F87">
-        <v>7353</v>
+        <v>2032</v>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t xml:space="preserve">311617388</t>
+          <t xml:space="preserve">311676080</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-07-27</t>
+          <t xml:space="preserve">2033-04-25</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
@@ -4381,25 +4381,25 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t xml:space="preserve">7137947</t>
+          <t xml:space="preserve">5445530</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="F88">
-        <v>3458</v>
+        <v>425</v>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t xml:space="preserve">311617330</t>
+          <t xml:space="preserve">311676080</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-07-27</t>
+          <t xml:space="preserve">2033-04-25</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
@@ -4431,7 +4431,7 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t xml:space="preserve">7089254</t>
+          <t xml:space="preserve">2657545</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
@@ -4440,16 +4440,16 @@
         </is>
       </c>
       <c r="F89">
-        <v>831</v>
+        <v>273</v>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t xml:space="preserve">311621564</t>
+          <t xml:space="preserve">311737864</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-08-19</t>
+          <t xml:space="preserve">2034-02-08</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
@@ -4481,7 +4481,7 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t xml:space="preserve">2657545</t>
+          <t xml:space="preserve">100725260</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
@@ -4490,16 +4490,16 @@
         </is>
       </c>
       <c r="F90">
-        <v>273</v>
+        <v>3640</v>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t xml:space="preserve">311734475</t>
+          <t xml:space="preserve">311852350</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-01-22</t>
+          <t xml:space="preserve">2035-08-29</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
@@ -4531,7 +4531,7 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t xml:space="preserve">100725260</t>
+          <t xml:space="preserve">2644084</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
@@ -4540,16 +4540,16 @@
         </is>
       </c>
       <c r="F91">
-        <v>3640</v>
+        <v>3173</v>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t xml:space="preserve">311852350</t>
+          <t xml:space="preserve">311887262</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-08-29</t>
+          <t xml:space="preserve">2036-02-17</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">

--- a/public/exports/29189706.xlsx
+++ b/public/exports/29189706.xlsx
@@ -9,7 +9,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:J97"/>
+  <dimension ref="A1:L97"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
@@ -29,35 +29,45 @@
       </c>
       <c r="D1" t="inlineStr">
         <is>
+          <t xml:space="preserve">Adresse</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Postnr.</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
           <t xml:space="preserve">BFE-nummer</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t xml:space="preserve">Bygningsnummer</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t xml:space="preserve">Areal (m²)</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t xml:space="preserve">EM-nummer</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldig til</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t xml:space="preserve">Status</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t xml:space="preserve">Mangler gyldigt mærke</t>
         </is>
@@ -81,33 +91,43 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
+          <t xml:space="preserve">Dalby Bygade 5</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5380</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
           <t xml:space="preserve">2642837</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="G2" t="inlineStr">
         <is>
           <t xml:space="preserve">6</t>
         </is>
       </c>
-      <c r="F2">
+      <c r="H2">
         <v>1764</v>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="I2" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="J2" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -131,33 +151,43 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
+          <t xml:space="preserve">Lindhøjvænget 1</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5330</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
           <t xml:space="preserve">2646560</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="G3" t="inlineStr">
         <is>
           <t xml:space="preserve">7</t>
         </is>
       </c>
-      <c r="F3">
+      <c r="H3">
         <v>795</v>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="I3" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="J3" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
+      <c r="K3" t="inlineStr">
         <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -181,33 +211,43 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
+          <t xml:space="preserve">Regnar Langesvej 1</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5300</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
           <t xml:space="preserve">5447821</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="G4" t="inlineStr">
         <is>
           <t xml:space="preserve">12</t>
         </is>
       </c>
-      <c r="F4">
+      <c r="H4">
         <v>345</v>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="I4" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
+      <c r="J4" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
+      <c r="K4" t="inlineStr">
         <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
+      <c r="L4" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -231,33 +271,43 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
+          <t xml:space="preserve">Dosseringen 13</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5300</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
           <t xml:space="preserve">726971, 5446776</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="G5" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F5">
+      <c r="H5">
         <v>318</v>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="I5" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
+      <c r="J5" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
+      <c r="K5" t="inlineStr">
         <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr">
+      <c r="L5" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -281,33 +331,43 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
+          <t xml:space="preserve">Dosseringen 35</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5300</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
           <t xml:space="preserve">726974, 5446779</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="G6" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F6">
+      <c r="H6">
         <v>1658</v>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="I6" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
+      <c r="J6" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
+      <c r="K6" t="inlineStr">
         <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr">
+      <c r="L6" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -331,33 +391,43 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
+          <t xml:space="preserve">Odensevej 48</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5300</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
           <t xml:space="preserve">727288, 9467816</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="G7" t="inlineStr">
         <is>
           <t xml:space="preserve">22</t>
         </is>
       </c>
-      <c r="F7">
+      <c r="H7">
         <v>680</v>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="I7" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
+      <c r="J7" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
+      <c r="K7" t="inlineStr">
         <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
+      <c r="L7" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -381,33 +451,43 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
+          <t xml:space="preserve">Søndre Havnekaj 10</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5300</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
           <t xml:space="preserve">727536, 7992424</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="G8" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F8">
+      <c r="H8">
         <v>600</v>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="I8" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
+      <c r="J8" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="I8" t="inlineStr">
+      <c r="K8" t="inlineStr">
         <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr">
+      <c r="L8" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -431,33 +511,43 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
+          <t xml:space="preserve">Marinavejen 12</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5300</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
           <t xml:space="preserve">727707, 5445271</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="G9" t="inlineStr">
         <is>
           <t xml:space="preserve">29</t>
         </is>
       </c>
-      <c r="F9">
+      <c r="H9">
         <v>1384</v>
       </c>
-      <c r="G9" t="inlineStr">
+      <c r="I9" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
+      <c r="J9" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="I9" t="inlineStr">
+      <c r="K9" t="inlineStr">
         <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="J9" t="inlineStr">
+      <c r="L9" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -481,33 +571,43 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
+          <t xml:space="preserve">Vejlevangen 18</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5300</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
           <t xml:space="preserve">727715, 5446764</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
+      <c r="G10" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F10">
+      <c r="H10">
         <v>356</v>
       </c>
-      <c r="G10" t="inlineStr">
+      <c r="I10" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
+      <c r="J10" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="I10" t="inlineStr">
+      <c r="K10" t="inlineStr">
         <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="J10" t="inlineStr">
+      <c r="L10" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -531,33 +631,43 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
+          <t xml:space="preserve">Grønlandsgade 1</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5300</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
           <t xml:space="preserve">727717, 5445867</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
+      <c r="G11" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F11">
+      <c r="H11">
         <v>456</v>
       </c>
-      <c r="G11" t="inlineStr">
+      <c r="I11" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="H11" t="inlineStr">
+      <c r="J11" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="I11" t="inlineStr">
+      <c r="K11" t="inlineStr">
         <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="J11" t="inlineStr">
+      <c r="L11" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -581,33 +691,43 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
+          <t xml:space="preserve">Margrethes Plads 1</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5300</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
           <t xml:space="preserve">7885723, 100938670</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
+      <c r="G12" t="inlineStr">
         <is>
           <t xml:space="preserve">6</t>
         </is>
       </c>
-      <c r="F12">
+      <c r="H12">
         <v>384</v>
       </c>
-      <c r="G12" t="inlineStr">
+      <c r="I12" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="H12" t="inlineStr">
+      <c r="J12" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="I12" t="inlineStr">
+      <c r="K12" t="inlineStr">
         <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="J12" t="inlineStr">
+      <c r="L12" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -631,33 +751,43 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
+          <t xml:space="preserve">Enggade 19</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5300</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
           <t xml:space="preserve">9467816</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
+      <c r="G13" t="inlineStr">
         <is>
           <t xml:space="preserve">145</t>
         </is>
       </c>
-      <c r="F13">
+      <c r="H13">
         <v>3083</v>
       </c>
-      <c r="G13" t="inlineStr">
+      <c r="I13" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="H13" t="inlineStr">
+      <c r="J13" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="I13" t="inlineStr">
+      <c r="K13" t="inlineStr">
         <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="J13" t="inlineStr">
+      <c r="L13" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -681,33 +811,43 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
+          <t xml:space="preserve">Enggade 19</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5300</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
           <t xml:space="preserve">9467816</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
+      <c r="G14" t="inlineStr">
         <is>
           <t xml:space="preserve">9</t>
         </is>
       </c>
-      <c r="F14">
+      <c r="H14">
         <v>1095</v>
       </c>
-      <c r="G14" t="inlineStr">
+      <c r="I14" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="H14" t="inlineStr">
+      <c r="J14" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="I14" t="inlineStr">
+      <c r="K14" t="inlineStr">
         <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="J14" t="inlineStr">
+      <c r="L14" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -731,33 +871,43 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
+          <t xml:space="preserve">Toften 600</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5330</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
           <t xml:space="preserve">2647308</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr">
+      <c r="G15" t="inlineStr">
         <is>
           <t xml:space="preserve">14</t>
         </is>
       </c>
-      <c r="F15">
+      <c r="H15">
         <v>922</v>
       </c>
-      <c r="G15" t="inlineStr">
+      <c r="I15" t="inlineStr">
         <is>
           <t xml:space="preserve">200015627</t>
         </is>
       </c>
-      <c r="H15" t="inlineStr">
+      <c r="J15" t="inlineStr">
         <is>
           <t xml:space="preserve">2019-06-23</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr">
+      <c r="K15" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="J15" t="inlineStr">
+      <c r="L15" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -781,33 +931,43 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
+          <t xml:space="preserve">Strandgade 5</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5300</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
           <t xml:space="preserve">5445177</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr">
+      <c r="G16" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F16">
+      <c r="H16">
         <v>301</v>
       </c>
-      <c r="G16" t="inlineStr">
+      <c r="I16" t="inlineStr">
         <is>
           <t xml:space="preserve">200016330</t>
         </is>
       </c>
-      <c r="H16" t="inlineStr">
+      <c r="J16" t="inlineStr">
         <is>
           <t xml:space="preserve">2019-06-29</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr">
+      <c r="K16" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="J16" t="inlineStr">
+      <c r="L16" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -831,33 +991,43 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
+          <t xml:space="preserve">Marinavejen 6</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5300</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
           <t xml:space="preserve">727708, 9281555</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr">
+      <c r="G17" t="inlineStr">
         <is>
           <t xml:space="preserve">15</t>
         </is>
       </c>
-      <c r="F17">
+      <c r="H17">
         <v>705</v>
       </c>
-      <c r="G17" t="inlineStr">
+      <c r="I17" t="inlineStr">
         <is>
           <t xml:space="preserve">310035433</t>
         </is>
       </c>
-      <c r="H17" t="inlineStr">
+      <c r="J17" t="inlineStr">
         <is>
           <t xml:space="preserve">2023-04-17</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr">
+      <c r="K17" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="J17" t="inlineStr">
+      <c r="L17" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -881,33 +1051,43 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
+          <t xml:space="preserve">Marinavejen 1</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5300</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
           <t xml:space="preserve">727740, 9281555</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr">
+      <c r="G18" t="inlineStr">
         <is>
           <t xml:space="preserve">13</t>
         </is>
       </c>
-      <c r="F18">
+      <c r="H18">
         <v>2179</v>
       </c>
-      <c r="G18" t="inlineStr">
+      <c r="I18" t="inlineStr">
         <is>
           <t xml:space="preserve">311063628</t>
         </is>
       </c>
-      <c r="H18" t="inlineStr">
+      <c r="J18" t="inlineStr">
         <is>
           <t xml:space="preserve">2024-07-07</t>
         </is>
       </c>
-      <c r="I18" t="inlineStr">
+      <c r="K18" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="J18" t="inlineStr">
+      <c r="L18" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -931,33 +1111,43 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
+          <t xml:space="preserve">Toften 600</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5330</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
           <t xml:space="preserve">2647308</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr">
+      <c r="G19" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F19">
+      <c r="H19">
         <v>1815</v>
       </c>
-      <c r="G19" t="inlineStr">
+      <c r="I19" t="inlineStr">
         <is>
           <t xml:space="preserve">311289781</t>
         </is>
       </c>
-      <c r="H19" t="inlineStr">
+      <c r="J19" t="inlineStr">
         <is>
           <t xml:space="preserve">2027-12-20</t>
         </is>
       </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
+      <c r="K19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -981,33 +1171,43 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
+          <t xml:space="preserve">Grønvangen 32</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5550</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
           <t xml:space="preserve">100059307</t>
         </is>
       </c>
-      <c r="E20" t="inlineStr">
+      <c r="G20" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F20">
+      <c r="H20">
         <v>2301</v>
       </c>
-      <c r="G20" t="inlineStr">
+      <c r="I20" t="inlineStr">
         <is>
           <t xml:space="preserve">311483550</t>
         </is>
       </c>
-      <c r="H20" t="inlineStr">
+      <c r="J20" t="inlineStr">
         <is>
           <t xml:space="preserve">2030-12-17</t>
         </is>
       </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
+      <c r="K20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1031,33 +1231,43 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
+          <t xml:space="preserve">Dalby Bygade 5</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5380</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
           <t xml:space="preserve">2642837</t>
         </is>
       </c>
-      <c r="E21" t="inlineStr">
+      <c r="G21" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F21">
+      <c r="H21">
         <v>662</v>
       </c>
-      <c r="G21" t="inlineStr">
+      <c r="I21" t="inlineStr">
         <is>
           <t xml:space="preserve">311495046</t>
         </is>
       </c>
-      <c r="H21" t="inlineStr">
+      <c r="J21" t="inlineStr">
         <is>
           <t xml:space="preserve">2031-02-12</t>
         </is>
       </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
+      <c r="K21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1081,33 +1291,43 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
+          <t xml:space="preserve">Dalby Bygade 5</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5380</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
           <t xml:space="preserve">2642837</t>
         </is>
       </c>
-      <c r="E22" t="inlineStr">
+      <c r="G22" t="inlineStr">
         <is>
           <t xml:space="preserve">4</t>
         </is>
       </c>
-      <c r="F22">
+      <c r="H22">
         <v>2794</v>
       </c>
-      <c r="G22" t="inlineStr">
+      <c r="I22" t="inlineStr">
         <is>
           <t xml:space="preserve">311495046</t>
         </is>
       </c>
-      <c r="H22" t="inlineStr">
+      <c r="J22" t="inlineStr">
         <is>
           <t xml:space="preserve">2031-02-12</t>
         </is>
       </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
+      <c r="K22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1131,33 +1351,43 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
+          <t xml:space="preserve">Dalby Bygade 5</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5380</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
           <t xml:space="preserve">2642837</t>
         </is>
       </c>
-      <c r="E23" t="inlineStr">
+      <c r="G23" t="inlineStr">
         <is>
           <t xml:space="preserve">9</t>
         </is>
       </c>
-      <c r="F23">
+      <c r="H23">
         <v>314</v>
       </c>
-      <c r="G23" t="inlineStr">
+      <c r="I23" t="inlineStr">
         <is>
           <t xml:space="preserve">311495046</t>
         </is>
       </c>
-      <c r="H23" t="inlineStr">
+      <c r="J23" t="inlineStr">
         <is>
           <t xml:space="preserve">2031-02-12</t>
         </is>
       </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
+      <c r="K23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1181,33 +1411,43 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
+          <t xml:space="preserve">Askvej 24</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5300</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
           <t xml:space="preserve">5447028</t>
         </is>
       </c>
-      <c r="E24" t="inlineStr">
+      <c r="G24" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F24">
+      <c r="H24">
         <v>543</v>
       </c>
-      <c r="G24" t="inlineStr">
+      <c r="I24" t="inlineStr">
         <is>
           <t xml:space="preserve">311497381</t>
         </is>
       </c>
-      <c r="H24" t="inlineStr">
+      <c r="J24" t="inlineStr">
         <is>
           <t xml:space="preserve">2031-02-22</t>
         </is>
       </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
+      <c r="K24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1231,33 +1471,43 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
+          <t xml:space="preserve">Borgmester Hansensvej 7</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5300</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
           <t xml:space="preserve">8573246</t>
         </is>
       </c>
-      <c r="E25" t="inlineStr">
+      <c r="G25" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F25">
+      <c r="H25">
         <v>5771</v>
       </c>
-      <c r="G25" t="inlineStr">
+      <c r="I25" t="inlineStr">
         <is>
           <t xml:space="preserve">311497472</t>
         </is>
       </c>
-      <c r="H25" t="inlineStr">
+      <c r="J25" t="inlineStr">
         <is>
           <t xml:space="preserve">2031-02-22</t>
         </is>
       </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
+      <c r="K25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1281,33 +1531,43 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
+          <t xml:space="preserve">Børmosevej 5</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5550</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
           <t xml:space="preserve">727744, 7137947</t>
         </is>
       </c>
-      <c r="E26" t="inlineStr">
+      <c r="G26" t="inlineStr">
         <is>
           <t xml:space="preserve">8</t>
         </is>
       </c>
-      <c r="F26">
+      <c r="H26">
         <v>752</v>
       </c>
-      <c r="G26" t="inlineStr">
+      <c r="I26" t="inlineStr">
         <is>
           <t xml:space="preserve">311498092</t>
         </is>
       </c>
-      <c r="H26" t="inlineStr">
+      <c r="J26" t="inlineStr">
         <is>
           <t xml:space="preserve">2031-02-24</t>
         </is>
       </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
+      <c r="K26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1331,33 +1591,43 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
+          <t xml:space="preserve">Fabers Alle 4</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5300</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
           <t xml:space="preserve">100044506</t>
         </is>
       </c>
-      <c r="E27" t="inlineStr">
+      <c r="G27" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F27">
+      <c r="H27">
         <v>285</v>
       </c>
-      <c r="G27" t="inlineStr">
+      <c r="I27" t="inlineStr">
         <is>
           <t xml:space="preserve">311505577</t>
         </is>
       </c>
-      <c r="H27" t="inlineStr">
+      <c r="J27" t="inlineStr">
         <is>
           <t xml:space="preserve">2031-03-22</t>
         </is>
       </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
+      <c r="K27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1381,33 +1651,43 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
+          <t xml:space="preserve">Lindøalleen 77</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5330</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
           <t xml:space="preserve">1329020</t>
         </is>
       </c>
-      <c r="E28" t="inlineStr">
+      <c r="G28" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F28">
+      <c r="H28">
         <v>2329</v>
       </c>
-      <c r="G28" t="inlineStr">
+      <c r="I28" t="inlineStr">
         <is>
           <t xml:space="preserve">311505625</t>
         </is>
       </c>
-      <c r="H28" t="inlineStr">
+      <c r="J28" t="inlineStr">
         <is>
           <t xml:space="preserve">2031-03-22</t>
         </is>
       </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
+      <c r="K28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1431,33 +1711,43 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
+          <t xml:space="preserve">Fynshovedvej 486E</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5390</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
           <t xml:space="preserve">2649327</t>
         </is>
       </c>
-      <c r="E29" t="inlineStr">
+      <c r="G29" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F29">
+      <c r="H29">
         <v>919</v>
       </c>
-      <c r="G29" t="inlineStr">
+      <c r="I29" t="inlineStr">
         <is>
           <t xml:space="preserve">311505590</t>
         </is>
       </c>
-      <c r="H29" t="inlineStr">
+      <c r="J29" t="inlineStr">
         <is>
           <t xml:space="preserve">2031-03-22</t>
         </is>
       </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr">
+      <c r="K29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1481,33 +1771,43 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
+          <t xml:space="preserve">Gyldenlund 1</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5550</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
           <t xml:space="preserve">2657334</t>
         </is>
       </c>
-      <c r="E30" t="inlineStr">
+      <c r="G30" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F30">
+      <c r="H30">
         <v>1008</v>
       </c>
-      <c r="G30" t="inlineStr">
+      <c r="I30" t="inlineStr">
         <is>
           <t xml:space="preserve">311505605</t>
         </is>
       </c>
-      <c r="H30" t="inlineStr">
+      <c r="J30" t="inlineStr">
         <is>
           <t xml:space="preserve">2031-03-22</t>
         </is>
       </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr">
+      <c r="K30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1531,33 +1831,43 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
+          <t xml:space="preserve">Hans Schacksvej 4</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5300</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
           <t xml:space="preserve">5445095</t>
         </is>
       </c>
-      <c r="E31" t="inlineStr">
+      <c r="G31" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F31">
+      <c r="H31">
         <v>2098</v>
       </c>
-      <c r="G31" t="inlineStr">
+      <c r="I31" t="inlineStr">
         <is>
           <t xml:space="preserve">311505621</t>
         </is>
       </c>
-      <c r="H31" t="inlineStr">
+      <c r="J31" t="inlineStr">
         <is>
           <t xml:space="preserve">2031-03-22</t>
         </is>
       </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr">
+      <c r="K31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1581,33 +1891,43 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
+          <t xml:space="preserve">Grønnegårds Alle 2</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5300</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
           <t xml:space="preserve">8045593</t>
         </is>
       </c>
-      <c r="E32" t="inlineStr">
+      <c r="G32" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F32">
+      <c r="H32">
         <v>582</v>
       </c>
-      <c r="G32" t="inlineStr">
+      <c r="I32" t="inlineStr">
         <is>
           <t xml:space="preserve">311505594</t>
         </is>
       </c>
-      <c r="H32" t="inlineStr">
+      <c r="J32" t="inlineStr">
         <is>
           <t xml:space="preserve">2031-03-22</t>
         </is>
       </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr">
+      <c r="K32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1631,33 +1951,43 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
+          <t xml:space="preserve">Hans Tausensgade 29</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5550</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
           <t xml:space="preserve">2642378</t>
         </is>
       </c>
-      <c r="E33" t="inlineStr">
+      <c r="G33" t="inlineStr">
         <is>
           <t xml:space="preserve">2</t>
         </is>
       </c>
-      <c r="F33">
+      <c r="H33">
         <v>344</v>
       </c>
-      <c r="G33" t="inlineStr">
+      <c r="I33" t="inlineStr">
         <is>
           <t xml:space="preserve">311518199</t>
         </is>
       </c>
-      <c r="H33" t="inlineStr">
+      <c r="J33" t="inlineStr">
         <is>
           <t xml:space="preserve">2031-05-06</t>
         </is>
       </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr">
+      <c r="K33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1681,33 +2011,43 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
+          <t xml:space="preserve">Hans Tausensgade 29</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5550</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
           <t xml:space="preserve">2642378</t>
         </is>
       </c>
-      <c r="E34" t="inlineStr">
+      <c r="G34" t="inlineStr">
         <is>
           <t xml:space="preserve">5</t>
         </is>
       </c>
-      <c r="F34">
+      <c r="H34">
         <v>1019</v>
       </c>
-      <c r="G34" t="inlineStr">
+      <c r="I34" t="inlineStr">
         <is>
           <t xml:space="preserve">311518199</t>
         </is>
       </c>
-      <c r="H34" t="inlineStr">
+      <c r="J34" t="inlineStr">
         <is>
           <t xml:space="preserve">2031-05-06</t>
         </is>
       </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J34" t="inlineStr">
+      <c r="K34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1731,33 +2071,43 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
+          <t xml:space="preserve">Bispehaven 48</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5550</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
           <t xml:space="preserve">2642402</t>
         </is>
       </c>
-      <c r="E35" t="inlineStr">
+      <c r="G35" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F35">
+      <c r="H35">
         <v>260</v>
       </c>
-      <c r="G35" t="inlineStr">
+      <c r="I35" t="inlineStr">
         <is>
           <t xml:space="preserve">311598345</t>
         </is>
       </c>
-      <c r="H35" t="inlineStr">
+      <c r="J35" t="inlineStr">
         <is>
           <t xml:space="preserve">2031-05-06</t>
         </is>
       </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J35" t="inlineStr">
+      <c r="K35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1781,33 +2131,43 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
+          <t xml:space="preserve">Birkeparken 13</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5550</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
           <t xml:space="preserve">2658030</t>
         </is>
       </c>
-      <c r="E36" t="inlineStr">
+      <c r="G36" t="inlineStr">
         <is>
           <t xml:space="preserve">6</t>
         </is>
       </c>
-      <c r="F36">
+      <c r="H36">
         <v>260</v>
       </c>
-      <c r="G36" t="inlineStr">
+      <c r="I36" t="inlineStr">
         <is>
           <t xml:space="preserve">311518262</t>
         </is>
       </c>
-      <c r="H36" t="inlineStr">
+      <c r="J36" t="inlineStr">
         <is>
           <t xml:space="preserve">2031-05-06</t>
         </is>
       </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J36" t="inlineStr">
+      <c r="K36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1831,33 +2191,43 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
+          <t xml:space="preserve">Kristine Rudesvej 23</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5300</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
           <t xml:space="preserve">5446101</t>
         </is>
       </c>
-      <c r="E37" t="inlineStr">
+      <c r="G37" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F37">
+      <c r="H37">
         <v>1797</v>
       </c>
-      <c r="G37" t="inlineStr">
+      <c r="I37" t="inlineStr">
         <is>
           <t xml:space="preserve">311518286</t>
         </is>
       </c>
-      <c r="H37" t="inlineStr">
+      <c r="J37" t="inlineStr">
         <is>
           <t xml:space="preserve">2031-05-06</t>
         </is>
       </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J37" t="inlineStr">
+      <c r="K37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1881,33 +2251,43 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
+          <t xml:space="preserve">Borgmester Hansensvej 3</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5300</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
           <t xml:space="preserve">5446234</t>
         </is>
       </c>
-      <c r="E38" t="inlineStr">
+      <c r="G38" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F38">
+      <c r="H38">
         <v>1516</v>
       </c>
-      <c r="G38" t="inlineStr">
+      <c r="I38" t="inlineStr">
         <is>
           <t xml:space="preserve">311518290</t>
         </is>
       </c>
-      <c r="H38" t="inlineStr">
+      <c r="J38" t="inlineStr">
         <is>
           <t xml:space="preserve">2031-05-06</t>
         </is>
       </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J38" t="inlineStr">
+      <c r="K38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1931,33 +2311,43 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
+          <t xml:space="preserve">Kohaven 8</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5300</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
           <t xml:space="preserve">5446917</t>
         </is>
       </c>
-      <c r="E39" t="inlineStr">
+      <c r="G39" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F39">
+      <c r="H39">
         <v>923</v>
       </c>
-      <c r="G39" t="inlineStr">
+      <c r="I39" t="inlineStr">
         <is>
           <t xml:space="preserve">311518236</t>
         </is>
       </c>
-      <c r="H39" t="inlineStr">
+      <c r="J39" t="inlineStr">
         <is>
           <t xml:space="preserve">2031-05-06</t>
         </is>
       </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J39" t="inlineStr">
+      <c r="K39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1981,33 +2371,43 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rosendalen 215</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5330</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
           <t xml:space="preserve">2646524</t>
         </is>
       </c>
-      <c r="E40" t="inlineStr">
+      <c r="G40" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F40">
+      <c r="H40">
         <v>362</v>
       </c>
-      <c r="G40" t="inlineStr">
+      <c r="I40" t="inlineStr">
         <is>
           <t xml:space="preserve">311526236</t>
         </is>
       </c>
-      <c r="H40" t="inlineStr">
+      <c r="J40" t="inlineStr">
         <is>
           <t xml:space="preserve">2031-06-08</t>
         </is>
       </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J40" t="inlineStr">
+      <c r="K40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2031,33 +2431,43 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
+          <t xml:space="preserve">Lavindsgårdsvej 7</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5550</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
           <t xml:space="preserve">2657922</t>
         </is>
       </c>
-      <c r="E41" t="inlineStr">
+      <c r="G41" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F41">
+      <c r="H41">
         <v>3580</v>
       </c>
-      <c r="G41" t="inlineStr">
-        <is>
-          <t xml:space="preserve">311526226</t>
-        </is>
-      </c>
-      <c r="H41" t="inlineStr">
+      <c r="I41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">311526227</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
         <is>
           <t xml:space="preserve">2031-06-08</t>
         </is>
       </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J41" t="inlineStr">
+      <c r="K41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2081,33 +2491,43 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
+          <t xml:space="preserve">Lindhøjvej 2</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5330</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
           <t xml:space="preserve">7771570</t>
         </is>
       </c>
-      <c r="E42" t="inlineStr">
+      <c r="G42" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F42">
+      <c r="H42">
         <v>4136</v>
       </c>
-      <c r="G42" t="inlineStr">
+      <c r="I42" t="inlineStr">
         <is>
           <t xml:space="preserve">311526259</t>
         </is>
       </c>
-      <c r="H42" t="inlineStr">
+      <c r="J42" t="inlineStr">
         <is>
           <t xml:space="preserve">2031-06-08</t>
         </is>
       </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J42" t="inlineStr">
+      <c r="K42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2131,33 +2551,43 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
+          <t xml:space="preserve">Lindøalleen 51</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5330</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
           <t xml:space="preserve">2646560</t>
         </is>
       </c>
-      <c r="E43" t="inlineStr">
+      <c r="G43" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F43">
+      <c r="H43">
         <v>7542</v>
       </c>
-      <c r="G43" t="inlineStr">
+      <c r="I43" t="inlineStr">
         <is>
           <t xml:space="preserve">311540126</t>
         </is>
       </c>
-      <c r="H43" t="inlineStr">
+      <c r="J43" t="inlineStr">
         <is>
           <t xml:space="preserve">2031-08-11</t>
         </is>
       </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J43" t="inlineStr">
+      <c r="K43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2181,33 +2611,43 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
+          <t xml:space="preserve">Lindøalleen 53</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5330</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
           <t xml:space="preserve">2646560</t>
         </is>
       </c>
-      <c r="E44" t="inlineStr">
+      <c r="G44" t="inlineStr">
         <is>
           <t xml:space="preserve">2</t>
         </is>
       </c>
-      <c r="F44">
+      <c r="H44">
         <v>1970</v>
       </c>
-      <c r="G44" t="inlineStr">
+      <c r="I44" t="inlineStr">
         <is>
           <t xml:space="preserve">311540105</t>
         </is>
       </c>
-      <c r="H44" t="inlineStr">
+      <c r="J44" t="inlineStr">
         <is>
           <t xml:space="preserve">2031-08-11</t>
         </is>
       </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J44" t="inlineStr">
+      <c r="K44" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2231,33 +2671,43 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
+          <t xml:space="preserve">Lindøalleen 47</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5330</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
           <t xml:space="preserve">2646560</t>
         </is>
       </c>
-      <c r="E45" t="inlineStr">
+      <c r="G45" t="inlineStr">
         <is>
           <t xml:space="preserve">4</t>
         </is>
       </c>
-      <c r="F45">
+      <c r="H45">
         <v>526</v>
       </c>
-      <c r="G45" t="inlineStr">
+      <c r="I45" t="inlineStr">
         <is>
           <t xml:space="preserve">311540125</t>
         </is>
       </c>
-      <c r="H45" t="inlineStr">
+      <c r="J45" t="inlineStr">
         <is>
           <t xml:space="preserve">2031-08-11</t>
         </is>
       </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J45" t="inlineStr">
+      <c r="K45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2281,33 +2731,43 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
+          <t xml:space="preserve">Marinavejen 2</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5300</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
           <t xml:space="preserve">727703, 9281555</t>
         </is>
       </c>
-      <c r="E46" t="inlineStr">
+      <c r="G46" t="inlineStr">
         <is>
           <t xml:space="preserve">9</t>
         </is>
       </c>
-      <c r="F46">
+      <c r="H46">
         <v>374</v>
       </c>
-      <c r="G46" t="inlineStr">
+      <c r="I46" t="inlineStr">
         <is>
           <t xml:space="preserve">311545701</t>
         </is>
       </c>
-      <c r="H46" t="inlineStr">
+      <c r="J46" t="inlineStr">
         <is>
           <t xml:space="preserve">2031-09-03</t>
         </is>
       </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J46" t="inlineStr">
+      <c r="K46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2331,33 +2791,43 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
+          <t xml:space="preserve">Nymarken 47</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5300</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
           <t xml:space="preserve">2647942</t>
         </is>
       </c>
-      <c r="E47" t="inlineStr">
+      <c r="G47" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F47">
+      <c r="H47">
         <v>3098</v>
       </c>
-      <c r="G47" t="inlineStr">
+      <c r="I47" t="inlineStr">
         <is>
           <t xml:space="preserve">311557515</t>
         </is>
       </c>
-      <c r="H47" t="inlineStr">
+      <c r="J47" t="inlineStr">
         <is>
           <t xml:space="preserve">2031-10-26</t>
         </is>
       </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J47" t="inlineStr">
+      <c r="K47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2381,33 +2851,43 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
+          <t xml:space="preserve">Nymarken 47</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5300</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
           <t xml:space="preserve">2647942</t>
         </is>
       </c>
-      <c r="E48" t="inlineStr">
+      <c r="G48" t="inlineStr">
         <is>
           <t xml:space="preserve">10</t>
         </is>
       </c>
-      <c r="F48">
+      <c r="H48">
         <v>1047</v>
       </c>
-      <c r="G48" t="inlineStr">
+      <c r="I48" t="inlineStr">
         <is>
           <t xml:space="preserve">311557515</t>
         </is>
       </c>
-      <c r="H48" t="inlineStr">
+      <c r="J48" t="inlineStr">
         <is>
           <t xml:space="preserve">2031-10-26</t>
         </is>
       </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J48" t="inlineStr">
+      <c r="K48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2431,33 +2911,43 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
+          <t xml:space="preserve">Nymarken 47</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5300</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
           <t xml:space="preserve">2647942</t>
         </is>
       </c>
-      <c r="E49" t="inlineStr">
+      <c r="G49" t="inlineStr">
         <is>
           <t xml:space="preserve">3</t>
         </is>
       </c>
-      <c r="F49">
+      <c r="H49">
         <v>1557</v>
       </c>
-      <c r="G49" t="inlineStr">
+      <c r="I49" t="inlineStr">
         <is>
           <t xml:space="preserve">311557515</t>
         </is>
       </c>
-      <c r="H49" t="inlineStr">
+      <c r="J49" t="inlineStr">
         <is>
           <t xml:space="preserve">2031-10-26</t>
         </is>
       </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J49" t="inlineStr">
+      <c r="K49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2481,33 +2971,43 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
+          <t xml:space="preserve">Nymarken 47</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5300</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
           <t xml:space="preserve">2647942</t>
         </is>
       </c>
-      <c r="E50" t="inlineStr">
+      <c r="G50" t="inlineStr">
         <is>
           <t xml:space="preserve">4</t>
         </is>
       </c>
-      <c r="F50">
+      <c r="H50">
         <v>935</v>
       </c>
-      <c r="G50" t="inlineStr">
+      <c r="I50" t="inlineStr">
         <is>
           <t xml:space="preserve">311557515</t>
         </is>
       </c>
-      <c r="H50" t="inlineStr">
+      <c r="J50" t="inlineStr">
         <is>
           <t xml:space="preserve">2031-10-26</t>
         </is>
       </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J50" t="inlineStr">
+      <c r="K50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2531,33 +3031,43 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
+          <t xml:space="preserve">Børmosevej 3</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5550</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
           <t xml:space="preserve">7137947</t>
         </is>
       </c>
-      <c r="E51" t="inlineStr">
+      <c r="G51" t="inlineStr">
         <is>
           <t xml:space="preserve">6</t>
         </is>
       </c>
-      <c r="F51">
+      <c r="H51">
         <v>2407</v>
       </c>
-      <c r="G51" t="inlineStr">
+      <c r="I51" t="inlineStr">
         <is>
           <t xml:space="preserve">311586428</t>
         </is>
       </c>
-      <c r="H51" t="inlineStr">
+      <c r="J51" t="inlineStr">
         <is>
           <t xml:space="preserve">2032-03-18</t>
         </is>
       </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J51" t="inlineStr">
+      <c r="K51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2581,33 +3091,43 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
+          <t xml:space="preserve">Vestergade 98</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5300</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
           <t xml:space="preserve">5446281</t>
         </is>
       </c>
-      <c r="E52" t="inlineStr">
+      <c r="G52" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F52">
+      <c r="H52">
         <v>957</v>
       </c>
-      <c r="G52" t="inlineStr">
+      <c r="I52" t="inlineStr">
         <is>
           <t xml:space="preserve">311587820</t>
         </is>
       </c>
-      <c r="H52" t="inlineStr">
+      <c r="J52" t="inlineStr">
         <is>
           <t xml:space="preserve">2032-03-24</t>
         </is>
       </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J52" t="inlineStr">
+      <c r="K52" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2631,33 +3151,43 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
+          <t xml:space="preserve">Mesinge Bygade 53</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5370</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
           <t xml:space="preserve">2644386</t>
         </is>
       </c>
-      <c r="E53" t="inlineStr">
+      <c r="G53" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F53">
+      <c r="H53">
         <v>272</v>
       </c>
-      <c r="G53" t="inlineStr">
+      <c r="I53" t="inlineStr">
         <is>
           <t xml:space="preserve">311589703</t>
         </is>
       </c>
-      <c r="H53" t="inlineStr">
+      <c r="J53" t="inlineStr">
         <is>
           <t xml:space="preserve">2032-03-31</t>
         </is>
       </c>
-      <c r="I53" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J53" t="inlineStr">
+      <c r="K53" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2681,33 +3211,43 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
+          <t xml:space="preserve">Mesinge Bygade 53</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5370</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
           <t xml:space="preserve">2644386</t>
         </is>
       </c>
-      <c r="E54" t="inlineStr">
+      <c r="G54" t="inlineStr">
         <is>
           <t xml:space="preserve">6</t>
         </is>
       </c>
-      <c r="F54">
+      <c r="H54">
         <v>334</v>
       </c>
-      <c r="G54" t="inlineStr">
+      <c r="I54" t="inlineStr">
         <is>
           <t xml:space="preserve">311589703</t>
         </is>
       </c>
-      <c r="H54" t="inlineStr">
+      <c r="J54" t="inlineStr">
         <is>
           <t xml:space="preserve">2032-03-31</t>
         </is>
       </c>
-      <c r="I54" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J54" t="inlineStr">
+      <c r="K54" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2731,33 +3271,43 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
+          <t xml:space="preserve">Mesinge Bygade 51</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5370</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
           <t xml:space="preserve">2644386</t>
         </is>
       </c>
-      <c r="E55" t="inlineStr">
+      <c r="G55" t="inlineStr">
         <is>
           <t xml:space="preserve">2</t>
         </is>
       </c>
-      <c r="F55">
+      <c r="H55">
         <v>1673</v>
       </c>
-      <c r="G55" t="inlineStr">
+      <c r="I55" t="inlineStr">
         <is>
           <t xml:space="preserve">311590388</t>
         </is>
       </c>
-      <c r="H55" t="inlineStr">
+      <c r="J55" t="inlineStr">
         <is>
           <t xml:space="preserve">2032-04-04</t>
         </is>
       </c>
-      <c r="I55" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J55" t="inlineStr">
+      <c r="K55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2781,33 +3331,43 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
+          <t xml:space="preserve">Langegade 36</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5300</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
           <t xml:space="preserve">5445199</t>
         </is>
       </c>
-      <c r="E56" t="inlineStr">
+      <c r="G56" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F56">
+      <c r="H56">
         <v>426</v>
       </c>
-      <c r="G56" t="inlineStr">
+      <c r="I56" t="inlineStr">
         <is>
           <t xml:space="preserve">311590569</t>
         </is>
       </c>
-      <c r="H56" t="inlineStr">
+      <c r="J56" t="inlineStr">
         <is>
           <t xml:space="preserve">2032-04-04</t>
         </is>
       </c>
-      <c r="I56" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J56" t="inlineStr">
+      <c r="K56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L56" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2831,33 +3391,43 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
+          <t xml:space="preserve">Margrethes Plads 1</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5300</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
           <t xml:space="preserve">7885723</t>
         </is>
       </c>
-      <c r="E57" t="inlineStr">
+      <c r="G57" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F57">
+      <c r="H57">
         <v>1510</v>
       </c>
-      <c r="G57" t="inlineStr">
+      <c r="I57" t="inlineStr">
         <is>
           <t xml:space="preserve">311592215</t>
         </is>
       </c>
-      <c r="H57" t="inlineStr">
+      <c r="J57" t="inlineStr">
         <is>
           <t xml:space="preserve">2032-04-10</t>
         </is>
       </c>
-      <c r="I57" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J57" t="inlineStr">
+      <c r="K57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L57" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2881,33 +3451,43 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
+          <t xml:space="preserve">Skovsbovej 15</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5350</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
           <t xml:space="preserve">2648084</t>
         </is>
       </c>
-      <c r="E58" t="inlineStr">
+      <c r="G58" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F58">
+      <c r="H58">
         <v>1894</v>
       </c>
-      <c r="G58" t="inlineStr">
+      <c r="I58" t="inlineStr">
         <is>
           <t xml:space="preserve">311594782</t>
         </is>
       </c>
-      <c r="H58" t="inlineStr">
+      <c r="J58" t="inlineStr">
         <is>
           <t xml:space="preserve">2032-04-22</t>
         </is>
       </c>
-      <c r="I58" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J58" t="inlineStr">
+      <c r="K58" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L58" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2931,33 +3511,43 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
+          <t xml:space="preserve">Møtrikken 11</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5550</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
           <t xml:space="preserve">7136071</t>
         </is>
       </c>
-      <c r="E59" t="inlineStr">
+      <c r="G59" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F59">
+      <c r="H59">
         <v>703</v>
       </c>
-      <c r="G59" t="inlineStr">
+      <c r="I59" t="inlineStr">
         <is>
           <t xml:space="preserve">311595067</t>
         </is>
       </c>
-      <c r="H59" t="inlineStr">
+      <c r="J59" t="inlineStr">
         <is>
           <t xml:space="preserve">2032-04-25</t>
         </is>
       </c>
-      <c r="I59" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J59" t="inlineStr">
+      <c r="K59" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L59" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2981,33 +3571,43 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
+          <t xml:space="preserve">Nørregade 15</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5300</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
           <t xml:space="preserve">5445543</t>
         </is>
       </c>
-      <c r="E60" t="inlineStr">
+      <c r="G60" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F60">
+      <c r="H60">
         <v>338</v>
       </c>
-      <c r="G60" t="inlineStr">
+      <c r="I60" t="inlineStr">
         <is>
           <t xml:space="preserve">311596137</t>
         </is>
       </c>
-      <c r="H60" t="inlineStr">
+      <c r="J60" t="inlineStr">
         <is>
           <t xml:space="preserve">2032-04-28</t>
         </is>
       </c>
-      <c r="I60" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J60" t="inlineStr">
+      <c r="K60" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L60" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3031,33 +3631,43 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
+          <t xml:space="preserve">Andekæret 149</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5300</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
           <t xml:space="preserve">5447721</t>
         </is>
       </c>
-      <c r="E61" t="inlineStr">
+      <c r="G61" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F61">
+      <c r="H61">
         <v>658</v>
       </c>
-      <c r="G61" t="inlineStr">
-        <is>
-          <t xml:space="preserve">311597138</t>
-        </is>
-      </c>
-      <c r="H61" t="inlineStr">
+      <c r="I61" t="inlineStr">
+        <is>
+          <t xml:space="preserve">311597142</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
         <is>
           <t xml:space="preserve">2032-05-02</t>
         </is>
       </c>
-      <c r="I61" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J61" t="inlineStr">
+      <c r="K61" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L61" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3081,33 +3691,43 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
+          <t xml:space="preserve">Regnar Langesvej 1</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5300</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
           <t xml:space="preserve">5447821</t>
         </is>
       </c>
-      <c r="E62" t="inlineStr">
+      <c r="G62" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F62">
+      <c r="H62">
         <v>3067</v>
       </c>
-      <c r="G62" t="inlineStr">
+      <c r="I62" t="inlineStr">
         <is>
           <t xml:space="preserve">311597531</t>
         </is>
       </c>
-      <c r="H62" t="inlineStr">
+      <c r="J62" t="inlineStr">
         <is>
           <t xml:space="preserve">2032-05-03</t>
         </is>
       </c>
-      <c r="I62" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J62" t="inlineStr">
+      <c r="K62" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L62" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3131,33 +3751,43 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
+          <t xml:space="preserve">Strandgårds Alle 1</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5300</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
           <t xml:space="preserve">100063809</t>
         </is>
       </c>
-      <c r="E63" t="inlineStr">
+      <c r="G63" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F63">
+      <c r="H63">
         <v>1109</v>
       </c>
-      <c r="G63" t="inlineStr">
+      <c r="I63" t="inlineStr">
         <is>
           <t xml:space="preserve">311598079</t>
         </is>
       </c>
-      <c r="H63" t="inlineStr">
+      <c r="J63" t="inlineStr">
         <is>
           <t xml:space="preserve">2032-05-05</t>
         </is>
       </c>
-      <c r="I63" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J63" t="inlineStr">
+      <c r="K63" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L63" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3181,33 +3811,43 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
+          <t xml:space="preserve">Nymarken 45</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5300</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
           <t xml:space="preserve">2647942</t>
         </is>
       </c>
-      <c r="E64" t="inlineStr">
+      <c r="G64" t="inlineStr">
         <is>
           <t xml:space="preserve">8</t>
         </is>
       </c>
-      <c r="F64">
+      <c r="H64">
         <v>603</v>
       </c>
-      <c r="G64" t="inlineStr">
+      <c r="I64" t="inlineStr">
         <is>
           <t xml:space="preserve">311598123</t>
         </is>
       </c>
-      <c r="H64" t="inlineStr">
+      <c r="J64" t="inlineStr">
         <is>
           <t xml:space="preserve">2032-05-05</t>
         </is>
       </c>
-      <c r="I64" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J64" t="inlineStr">
+      <c r="K64" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L64" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3231,33 +3871,43 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
+          <t xml:space="preserve">Regnar Langesvej 3</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5300</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
           <t xml:space="preserve">5447821</t>
         </is>
       </c>
-      <c r="E65" t="inlineStr">
+      <c r="G65" t="inlineStr">
         <is>
           <t xml:space="preserve">6</t>
         </is>
       </c>
-      <c r="F65">
+      <c r="H65">
         <v>611</v>
       </c>
-      <c r="G65" t="inlineStr">
+      <c r="I65" t="inlineStr">
         <is>
           <t xml:space="preserve">311598741</t>
         </is>
       </c>
-      <c r="H65" t="inlineStr">
+      <c r="J65" t="inlineStr">
         <is>
           <t xml:space="preserve">2032-05-09</t>
         </is>
       </c>
-      <c r="I65" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J65" t="inlineStr">
+      <c r="K65" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L65" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3281,33 +3931,43 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
+          <t xml:space="preserve">Toften 600</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5330</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
           <t xml:space="preserve">2647308</t>
         </is>
       </c>
-      <c r="E66" t="inlineStr">
+      <c r="G66" t="inlineStr">
         <is>
           <t xml:space="preserve">2</t>
         </is>
       </c>
-      <c r="F66">
+      <c r="H66">
         <v>921</v>
       </c>
-      <c r="G66" t="inlineStr">
+      <c r="I66" t="inlineStr">
         <is>
           <t xml:space="preserve">311599005</t>
         </is>
       </c>
-      <c r="H66" t="inlineStr">
+      <c r="J66" t="inlineStr">
         <is>
           <t xml:space="preserve">2032-05-10</t>
         </is>
       </c>
-      <c r="I66" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J66" t="inlineStr">
+      <c r="K66" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L66" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3331,33 +3991,43 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
+          <t xml:space="preserve">Toften 600</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5330</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
           <t xml:space="preserve">2647308</t>
         </is>
       </c>
-      <c r="E67" t="inlineStr">
+      <c r="G67" t="inlineStr">
         <is>
           <t xml:space="preserve">3</t>
         </is>
       </c>
-      <c r="F67">
+      <c r="H67">
         <v>1104</v>
       </c>
-      <c r="G67" t="inlineStr">
+      <c r="I67" t="inlineStr">
         <is>
           <t xml:space="preserve">311599005</t>
         </is>
       </c>
-      <c r="H67" t="inlineStr">
+      <c r="J67" t="inlineStr">
         <is>
           <t xml:space="preserve">2032-05-10</t>
         </is>
       </c>
-      <c r="I67" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J67" t="inlineStr">
+      <c r="K67" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L67" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3381,33 +4051,43 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
+          <t xml:space="preserve">Toften 600</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5330</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
           <t xml:space="preserve">2647308</t>
         </is>
       </c>
-      <c r="E68" t="inlineStr">
+      <c r="G68" t="inlineStr">
         <is>
           <t xml:space="preserve">4</t>
         </is>
       </c>
-      <c r="F68">
+      <c r="H68">
         <v>679</v>
       </c>
-      <c r="G68" t="inlineStr">
+      <c r="I68" t="inlineStr">
         <is>
           <t xml:space="preserve">311599005</t>
         </is>
       </c>
-      <c r="H68" t="inlineStr">
+      <c r="J68" t="inlineStr">
         <is>
           <t xml:space="preserve">2032-05-10</t>
         </is>
       </c>
-      <c r="I68" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J68" t="inlineStr">
+      <c r="K68" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L68" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3431,33 +4111,43 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
+          <t xml:space="preserve">Toften 600</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5330</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
           <t xml:space="preserve">2647308</t>
         </is>
       </c>
-      <c r="E69" t="inlineStr">
+      <c r="G69" t="inlineStr">
         <is>
           <t xml:space="preserve">5</t>
         </is>
       </c>
-      <c r="F69">
+      <c r="H69">
         <v>487</v>
       </c>
-      <c r="G69" t="inlineStr">
+      <c r="I69" t="inlineStr">
         <is>
           <t xml:space="preserve">311599005</t>
         </is>
       </c>
-      <c r="H69" t="inlineStr">
+      <c r="J69" t="inlineStr">
         <is>
           <t xml:space="preserve">2032-05-10</t>
         </is>
       </c>
-      <c r="I69" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J69" t="inlineStr">
+      <c r="K69" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L69" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3481,33 +4171,43 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
+          <t xml:space="preserve">Marinavejen 8A</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5300</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
           <t xml:space="preserve">9281555</t>
         </is>
       </c>
-      <c r="E70" t="inlineStr">
+      <c r="G70" t="inlineStr">
         <is>
           <t xml:space="preserve">51</t>
         </is>
       </c>
-      <c r="F70">
+      <c r="H70">
         <v>256</v>
       </c>
-      <c r="G70" t="inlineStr">
+      <c r="I70" t="inlineStr">
         <is>
           <t xml:space="preserve">311600397</t>
         </is>
       </c>
-      <c r="H70" t="inlineStr">
+      <c r="J70" t="inlineStr">
         <is>
           <t xml:space="preserve">2032-05-16</t>
         </is>
       </c>
-      <c r="I70" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J70" t="inlineStr">
+      <c r="K70" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L70" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3531,33 +4231,43 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
+          <t xml:space="preserve">Marinavejen 4</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5300</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
           <t xml:space="preserve">9281555</t>
         </is>
       </c>
-      <c r="E71" t="inlineStr">
+      <c r="G71" t="inlineStr">
         <is>
           <t xml:space="preserve">53</t>
         </is>
       </c>
-      <c r="F71">
+      <c r="H71">
         <v>360</v>
       </c>
-      <c r="G71" t="inlineStr">
+      <c r="I71" t="inlineStr">
         <is>
           <t xml:space="preserve">311600401</t>
         </is>
       </c>
-      <c r="H71" t="inlineStr">
+      <c r="J71" t="inlineStr">
         <is>
           <t xml:space="preserve">2032-05-16</t>
         </is>
       </c>
-      <c r="I71" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J71" t="inlineStr">
+      <c r="K71" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L71" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3581,33 +4291,43 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
+          <t xml:space="preserve">Mosevangen 2</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5330</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
           <t xml:space="preserve">2647035</t>
         </is>
       </c>
-      <c r="E72" t="inlineStr">
+      <c r="G72" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F72">
+      <c r="H72">
         <v>2732</v>
       </c>
-      <c r="G72" t="inlineStr">
+      <c r="I72" t="inlineStr">
         <is>
           <t xml:space="preserve">311601059</t>
         </is>
       </c>
-      <c r="H72" t="inlineStr">
+      <c r="J72" t="inlineStr">
         <is>
           <t xml:space="preserve">2032-05-18</t>
         </is>
       </c>
-      <c r="I72" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J72" t="inlineStr">
+      <c r="K72" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L72" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3631,33 +4351,43 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
+          <t xml:space="preserve">Mosevangen 2</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5330</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
           <t xml:space="preserve">2647035</t>
         </is>
       </c>
-      <c r="E73" t="inlineStr">
+      <c r="G73" t="inlineStr">
         <is>
           <t xml:space="preserve">2</t>
         </is>
       </c>
-      <c r="F73">
+      <c r="H73">
         <v>1074</v>
       </c>
-      <c r="G73" t="inlineStr">
+      <c r="I73" t="inlineStr">
         <is>
           <t xml:space="preserve">311601058</t>
         </is>
       </c>
-      <c r="H73" t="inlineStr">
+      <c r="J73" t="inlineStr">
         <is>
           <t xml:space="preserve">2032-05-18</t>
         </is>
       </c>
-      <c r="I73" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J73" t="inlineStr">
+      <c r="K73" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L73" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3681,33 +4411,43 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
+          <t xml:space="preserve">Møllevej 6A</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5300</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
           <t xml:space="preserve">5445605</t>
         </is>
       </c>
-      <c r="E74" t="inlineStr">
+      <c r="G74" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F74">
+      <c r="H74">
         <v>1869</v>
       </c>
-      <c r="G74" t="inlineStr">
+      <c r="I74" t="inlineStr">
         <is>
           <t xml:space="preserve">311601070</t>
         </is>
       </c>
-      <c r="H74" t="inlineStr">
+      <c r="J74" t="inlineStr">
         <is>
           <t xml:space="preserve">2032-05-18</t>
         </is>
       </c>
-      <c r="I74" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J74" t="inlineStr">
+      <c r="K74" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L74" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3731,33 +4471,43 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
+          <t xml:space="preserve">Møllevej 61</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5300</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
           <t xml:space="preserve">5445605</t>
         </is>
       </c>
-      <c r="E75" t="inlineStr">
+      <c r="G75" t="inlineStr">
         <is>
           <t xml:space="preserve">2</t>
         </is>
       </c>
-      <c r="F75">
+      <c r="H75">
         <v>738</v>
       </c>
-      <c r="G75" t="inlineStr">
+      <c r="I75" t="inlineStr">
         <is>
           <t xml:space="preserve">311601070</t>
         </is>
       </c>
-      <c r="H75" t="inlineStr">
+      <c r="J75" t="inlineStr">
         <is>
           <t xml:space="preserve">2032-05-18</t>
         </is>
       </c>
-      <c r="I75" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J75" t="inlineStr">
+      <c r="K75" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L75" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3781,33 +4531,43 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
+          <t xml:space="preserve">Røjrupvej 9</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5550</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
           <t xml:space="preserve">2657345</t>
         </is>
       </c>
-      <c r="E76" t="inlineStr">
+      <c r="G76" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F76">
+      <c r="H76">
         <v>5119</v>
       </c>
-      <c r="G76" t="inlineStr">
+      <c r="I76" t="inlineStr">
         <is>
           <t xml:space="preserve">311602646</t>
         </is>
       </c>
-      <c r="H76" t="inlineStr">
+      <c r="J76" t="inlineStr">
         <is>
           <t xml:space="preserve">2032-05-24</t>
         </is>
       </c>
-      <c r="I76" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J76" t="inlineStr">
+      <c r="K76" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L76" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3831,33 +4591,43 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rønningevej 38</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5550</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
           <t xml:space="preserve">7137947</t>
         </is>
       </c>
-      <c r="E77" t="inlineStr">
+      <c r="G77" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F77">
+      <c r="H77">
         <v>573</v>
       </c>
-      <c r="G77" t="inlineStr">
+      <c r="I77" t="inlineStr">
         <is>
           <t xml:space="preserve">311604349</t>
         </is>
       </c>
-      <c r="H77" t="inlineStr">
+      <c r="J77" t="inlineStr">
         <is>
           <t xml:space="preserve">2032-05-31</t>
         </is>
       </c>
-      <c r="I77" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J77" t="inlineStr">
+      <c r="K77" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L77" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3881,33 +4651,43 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
+          <t xml:space="preserve">Lindøalleen 101</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5330</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
           <t xml:space="preserve">2645740</t>
         </is>
       </c>
-      <c r="E78" t="inlineStr">
+      <c r="G78" t="inlineStr">
         <is>
           <t xml:space="preserve">3</t>
         </is>
       </c>
-      <c r="F78">
+      <c r="H78">
         <v>324</v>
       </c>
-      <c r="G78" t="inlineStr">
+      <c r="I78" t="inlineStr">
         <is>
           <t xml:space="preserve">311616001</t>
         </is>
       </c>
-      <c r="H78" t="inlineStr">
+      <c r="J78" t="inlineStr">
         <is>
           <t xml:space="preserve">2032-07-18</t>
         </is>
       </c>
-      <c r="I78" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J78" t="inlineStr">
+      <c r="K78" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L78" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3931,33 +4711,43 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
+          <t xml:space="preserve">Lindøalleen 101</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5330</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
           <t xml:space="preserve">2645740</t>
         </is>
       </c>
-      <c r="E79" t="inlineStr">
+      <c r="G79" t="inlineStr">
         <is>
           <t xml:space="preserve">6</t>
         </is>
       </c>
-      <c r="F79">
+      <c r="H79">
         <v>350</v>
       </c>
-      <c r="G79" t="inlineStr">
+      <c r="I79" t="inlineStr">
         <is>
           <t xml:space="preserve">311616001</t>
         </is>
       </c>
-      <c r="H79" t="inlineStr">
+      <c r="J79" t="inlineStr">
         <is>
           <t xml:space="preserve">2032-07-18</t>
         </is>
       </c>
-      <c r="I79" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J79" t="inlineStr">
+      <c r="K79" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L79" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3981,33 +4771,43 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
+          <t xml:space="preserve">Lindøalleen 101</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5330</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
           <t xml:space="preserve">2645740</t>
         </is>
       </c>
-      <c r="E80" t="inlineStr">
+      <c r="G80" t="inlineStr">
         <is>
           <t xml:space="preserve">7</t>
         </is>
       </c>
-      <c r="F80">
+      <c r="H80">
         <v>742</v>
       </c>
-      <c r="G80" t="inlineStr">
+      <c r="I80" t="inlineStr">
         <is>
           <t xml:space="preserve">311616001</t>
         </is>
       </c>
-      <c r="H80" t="inlineStr">
+      <c r="J80" t="inlineStr">
         <is>
           <t xml:space="preserve">2032-07-18</t>
         </is>
       </c>
-      <c r="I80" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J80" t="inlineStr">
+      <c r="K80" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L80" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4031,33 +4831,43 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rønningevej 38</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5550</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
           <t xml:space="preserve">7137947</t>
         </is>
       </c>
-      <c r="E81" t="inlineStr">
+      <c r="G81" t="inlineStr">
         <is>
           <t xml:space="preserve">2</t>
         </is>
       </c>
-      <c r="F81">
+      <c r="H81">
         <v>7353</v>
       </c>
-      <c r="G81" t="inlineStr">
+      <c r="I81" t="inlineStr">
         <is>
           <t xml:space="preserve">311617388</t>
         </is>
       </c>
-      <c r="H81" t="inlineStr">
+      <c r="J81" t="inlineStr">
         <is>
           <t xml:space="preserve">2032-07-27</t>
         </is>
       </c>
-      <c r="I81" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J81" t="inlineStr">
+      <c r="K81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L81" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4081,33 +4891,43 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
+          <t xml:space="preserve">Børmosevej 3</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5550</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
           <t xml:space="preserve">7137947</t>
         </is>
       </c>
-      <c r="E82" t="inlineStr">
+      <c r="G82" t="inlineStr">
         <is>
           <t xml:space="preserve">3</t>
         </is>
       </c>
-      <c r="F82">
+      <c r="H82">
         <v>3458</v>
       </c>
-      <c r="G82" t="inlineStr">
+      <c r="I82" t="inlineStr">
         <is>
           <t xml:space="preserve">311617330</t>
         </is>
       </c>
-      <c r="H82" t="inlineStr">
+      <c r="J82" t="inlineStr">
         <is>
           <t xml:space="preserve">2032-07-27</t>
         </is>
       </c>
-      <c r="I82" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J82" t="inlineStr">
+      <c r="K82" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L82" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4131,33 +4951,43 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
+          <t xml:space="preserve">Strandvejen 41</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5300</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
           <t xml:space="preserve">7089254</t>
         </is>
       </c>
-      <c r="E83" t="inlineStr">
+      <c r="G83" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F83">
+      <c r="H83">
         <v>831</v>
       </c>
-      <c r="G83" t="inlineStr">
+      <c r="I83" t="inlineStr">
         <is>
           <t xml:space="preserve">311621564</t>
         </is>
       </c>
-      <c r="H83" t="inlineStr">
+      <c r="J83" t="inlineStr">
         <is>
           <t xml:space="preserve">2032-08-19</t>
         </is>
       </c>
-      <c r="I83" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J83" t="inlineStr">
+      <c r="K83" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L83" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4181,33 +5011,43 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
+          <t xml:space="preserve">Nørregade 21</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5300</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
           <t xml:space="preserve">5445530</t>
         </is>
       </c>
-      <c r="E84" t="inlineStr">
+      <c r="G84" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F84">
+      <c r="H84">
         <v>2330</v>
       </c>
-      <c r="G84" t="inlineStr">
+      <c r="I84" t="inlineStr">
         <is>
           <t xml:space="preserve">311676080</t>
         </is>
       </c>
-      <c r="H84" t="inlineStr">
+      <c r="J84" t="inlineStr">
         <is>
           <t xml:space="preserve">2033-04-25</t>
         </is>
       </c>
-      <c r="I84" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J84" t="inlineStr">
+      <c r="K84" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L84" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4231,33 +5071,43 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
+          <t xml:space="preserve">Nørregade 21</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5300</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
           <t xml:space="preserve">5445530</t>
         </is>
       </c>
-      <c r="E85" t="inlineStr">
+      <c r="G85" t="inlineStr">
         <is>
           <t xml:space="preserve">2</t>
         </is>
       </c>
-      <c r="F85">
+      <c r="H85">
         <v>1254</v>
       </c>
-      <c r="G85" t="inlineStr">
+      <c r="I85" t="inlineStr">
         <is>
           <t xml:space="preserve">311676080</t>
         </is>
       </c>
-      <c r="H85" t="inlineStr">
+      <c r="J85" t="inlineStr">
         <is>
           <t xml:space="preserve">2033-04-25</t>
         </is>
       </c>
-      <c r="I85" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J85" t="inlineStr">
+      <c r="K85" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L85" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4281,33 +5131,43 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
+          <t xml:space="preserve">Nørregade 21</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5300</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
           <t xml:space="preserve">5445530</t>
         </is>
       </c>
-      <c r="E86" t="inlineStr">
+      <c r="G86" t="inlineStr">
         <is>
           <t xml:space="preserve">3</t>
         </is>
       </c>
-      <c r="F86">
+      <c r="H86">
         <v>1521</v>
       </c>
-      <c r="G86" t="inlineStr">
+      <c r="I86" t="inlineStr">
         <is>
           <t xml:space="preserve">311676080</t>
         </is>
       </c>
-      <c r="H86" t="inlineStr">
+      <c r="J86" t="inlineStr">
         <is>
           <t xml:space="preserve">2033-04-25</t>
         </is>
       </c>
-      <c r="I86" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J86" t="inlineStr">
+      <c r="K86" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L86" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4331,33 +5191,43 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
+          <t xml:space="preserve">Nørregade 21</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5300</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
           <t xml:space="preserve">5445530</t>
         </is>
       </c>
-      <c r="E87" t="inlineStr">
+      <c r="G87" t="inlineStr">
         <is>
           <t xml:space="preserve">4</t>
         </is>
       </c>
-      <c r="F87">
+      <c r="H87">
         <v>2032</v>
       </c>
-      <c r="G87" t="inlineStr">
+      <c r="I87" t="inlineStr">
         <is>
           <t xml:space="preserve">311676080</t>
         </is>
       </c>
-      <c r="H87" t="inlineStr">
+      <c r="J87" t="inlineStr">
         <is>
           <t xml:space="preserve">2033-04-25</t>
         </is>
       </c>
-      <c r="I87" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J87" t="inlineStr">
+      <c r="K87" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L87" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4381,33 +5251,43 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
+          <t xml:space="preserve">Nørregade 21</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5300</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
           <t xml:space="preserve">5445530</t>
         </is>
       </c>
-      <c r="E88" t="inlineStr">
+      <c r="G88" t="inlineStr">
         <is>
           <t xml:space="preserve">5</t>
         </is>
       </c>
-      <c r="F88">
+      <c r="H88">
         <v>425</v>
       </c>
-      <c r="G88" t="inlineStr">
+      <c r="I88" t="inlineStr">
         <is>
           <t xml:space="preserve">311676080</t>
         </is>
       </c>
-      <c r="H88" t="inlineStr">
+      <c r="J88" t="inlineStr">
         <is>
           <t xml:space="preserve">2033-04-25</t>
         </is>
       </c>
-      <c r="I88" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J88" t="inlineStr">
+      <c r="K88" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L88" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4431,33 +5311,43 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
+          <t xml:space="preserve">Grønvej 12</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5550</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
           <t xml:space="preserve">2657545</t>
         </is>
       </c>
-      <c r="E89" t="inlineStr">
+      <c r="G89" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F89">
+      <c r="H89">
         <v>273</v>
       </c>
-      <c r="G89" t="inlineStr">
+      <c r="I89" t="inlineStr">
         <is>
           <t xml:space="preserve">311737864</t>
         </is>
       </c>
-      <c r="H89" t="inlineStr">
+      <c r="J89" t="inlineStr">
         <is>
           <t xml:space="preserve">2034-02-08</t>
         </is>
       </c>
-      <c r="I89" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J89" t="inlineStr">
+      <c r="K89" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L89" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4481,33 +5371,43 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
+          <t xml:space="preserve">Skovsbovej 14</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5350</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
           <t xml:space="preserve">100725260</t>
         </is>
       </c>
-      <c r="E90" t="inlineStr">
+      <c r="G90" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F90">
+      <c r="H90">
         <v>3640</v>
       </c>
-      <c r="G90" t="inlineStr">
+      <c r="I90" t="inlineStr">
         <is>
           <t xml:space="preserve">311852350</t>
         </is>
       </c>
-      <c r="H90" t="inlineStr">
+      <c r="J90" t="inlineStr">
         <is>
           <t xml:space="preserve">2035-08-29</t>
         </is>
       </c>
-      <c r="I90" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J90" t="inlineStr">
+      <c r="K90" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L90" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4531,33 +5431,43 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
+          <t xml:space="preserve">Marslev Byvej 41</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5290</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
           <t xml:space="preserve">2644084</t>
         </is>
       </c>
-      <c r="E91" t="inlineStr">
+      <c r="G91" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F91">
+      <c r="H91">
         <v>3173</v>
       </c>
-      <c r="G91" t="inlineStr">
+      <c r="I91" t="inlineStr">
         <is>
           <t xml:space="preserve">311887262</t>
         </is>
       </c>
-      <c r="H91" t="inlineStr">
+      <c r="J91" t="inlineStr">
         <is>
           <t xml:space="preserve">2036-02-17</t>
         </is>
       </c>
-      <c r="I91" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J91" t="inlineStr">
+      <c r="K91" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L91" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4581,33 +5491,43 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
+          <t xml:space="preserve">Fjordvej 162</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5330</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
           <t xml:space="preserve">2645809</t>
         </is>
       </c>
-      <c r="E92" t="inlineStr">
+      <c r="G92" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F92">
+      <c r="H92">
         <v>2060</v>
       </c>
-      <c r="G92" t="inlineStr">
+      <c r="I92" t="inlineStr">
         <is>
           <t xml:space="preserve">311884217</t>
         </is>
       </c>
-      <c r="H92" t="inlineStr">
+      <c r="J92" t="inlineStr">
         <is>
           <t xml:space="preserve">2036-02-25</t>
         </is>
       </c>
-      <c r="I92" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J92" t="inlineStr">
+      <c r="K92" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L92" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4631,33 +5551,43 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
+          <t xml:space="preserve">Fjordvej 162</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5330</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
           <t xml:space="preserve">2645809</t>
         </is>
       </c>
-      <c r="E93" t="inlineStr">
+      <c r="G93" t="inlineStr">
         <is>
           <t xml:space="preserve">2</t>
         </is>
       </c>
-      <c r="F93">
+      <c r="H93">
         <v>626</v>
       </c>
-      <c r="G93" t="inlineStr">
+      <c r="I93" t="inlineStr">
         <is>
           <t xml:space="preserve">311884217</t>
         </is>
       </c>
-      <c r="H93" t="inlineStr">
+      <c r="J93" t="inlineStr">
         <is>
           <t xml:space="preserve">2036-02-25</t>
         </is>
       </c>
-      <c r="I93" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J93" t="inlineStr">
+      <c r="K93" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L93" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4681,33 +5611,43 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
+          <t xml:space="preserve">Fjordvej 162</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5330</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
           <t xml:space="preserve">2645809</t>
         </is>
       </c>
-      <c r="E94" t="inlineStr">
+      <c r="G94" t="inlineStr">
         <is>
           <t xml:space="preserve">3</t>
         </is>
       </c>
-      <c r="F94">
+      <c r="H94">
         <v>1794</v>
       </c>
-      <c r="G94" t="inlineStr">
+      <c r="I94" t="inlineStr">
         <is>
           <t xml:space="preserve">311884217</t>
         </is>
       </c>
-      <c r="H94" t="inlineStr">
+      <c r="J94" t="inlineStr">
         <is>
           <t xml:space="preserve">2036-02-25</t>
         </is>
       </c>
-      <c r="I94" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J94" t="inlineStr">
+      <c r="K94" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L94" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4731,33 +5671,43 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
+          <t xml:space="preserve">Fjordvej 162</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5330</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
           <t xml:space="preserve">2645809</t>
         </is>
       </c>
-      <c r="E95" t="inlineStr">
+      <c r="G95" t="inlineStr">
         <is>
           <t xml:space="preserve">4</t>
         </is>
       </c>
-      <c r="F95">
+      <c r="H95">
         <v>313</v>
       </c>
-      <c r="G95" t="inlineStr">
+      <c r="I95" t="inlineStr">
         <is>
           <t xml:space="preserve">311884217</t>
         </is>
       </c>
-      <c r="H95" t="inlineStr">
+      <c r="J95" t="inlineStr">
         <is>
           <t xml:space="preserve">2036-02-25</t>
         </is>
       </c>
-      <c r="I95" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J95" t="inlineStr">
+      <c r="K95" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L95" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4781,33 +5731,43 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
+          <t xml:space="preserve">Fjordvej 162</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5330</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
           <t xml:space="preserve">2645809</t>
         </is>
       </c>
-      <c r="E96" t="inlineStr">
+      <c r="G96" t="inlineStr">
         <is>
           <t xml:space="preserve">5</t>
         </is>
       </c>
-      <c r="F96">
+      <c r="H96">
         <v>2813</v>
       </c>
-      <c r="G96" t="inlineStr">
+      <c r="I96" t="inlineStr">
         <is>
           <t xml:space="preserve">311884217</t>
         </is>
       </c>
-      <c r="H96" t="inlineStr">
+      <c r="J96" t="inlineStr">
         <is>
           <t xml:space="preserve">2036-02-25</t>
         </is>
       </c>
-      <c r="I96" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J96" t="inlineStr">
+      <c r="K96" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L96" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4831,39 +5791,49 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
+          <t xml:space="preserve">Margrethes Plads 1</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5300</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
           <t xml:space="preserve">7885723, 100938670</t>
         </is>
       </c>
-      <c r="E97" t="inlineStr">
+      <c r="G97" t="inlineStr">
         <is>
           <t xml:space="preserve">5</t>
         </is>
       </c>
-      <c r="F97">
+      <c r="H97">
         <v>809</v>
       </c>
-      <c r="G97" t="inlineStr">
+      <c r="I97" t="inlineStr">
         <is>
           <t xml:space="preserve">311911861</t>
         </is>
       </c>
-      <c r="H97" t="inlineStr">
+      <c r="J97" t="inlineStr">
         <is>
           <t xml:space="preserve">2036-06-30</t>
         </is>
       </c>
-      <c r="I97" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J97" t="inlineStr">
+      <c r="K97" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L97" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J97"/>
+  <autoFilter ref="A1:L97"/>
 </worksheet>
 </file>
--- a/public/exports/29189706.xlsx
+++ b/public/exports/29189706.xlsx
@@ -151,26 +151,26 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lindhøjvænget 1</t>
+          <t xml:space="preserve">Dosseringen 13</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t xml:space="preserve">5330</t>
+          <t xml:space="preserve">5300</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2646560</t>
+          <t xml:space="preserve">726971, 5446776</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H3">
-        <v>795</v>
+        <v>318</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -211,7 +211,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Regnar Langesvej 1</t>
+          <t xml:space="preserve">Dosseringen 35</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -221,16 +221,16 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t xml:space="preserve">5447821</t>
+          <t xml:space="preserve">726974, 5446779</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t xml:space="preserve">12</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H4">
-        <v>345</v>
+        <v>1658</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -271,7 +271,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dosseringen 13</t>
+          <t xml:space="preserve">Enggade 19</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -281,16 +281,16 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t xml:space="preserve">726971, 5446776</t>
+          <t xml:space="preserve">9467816</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">145</t>
         </is>
       </c>
       <c r="H5">
-        <v>318</v>
+        <v>3083</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -331,7 +331,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dosseringen 35</t>
+          <t xml:space="preserve">Enggade 19</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -341,16 +341,16 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t xml:space="preserve">726974, 5446779</t>
+          <t xml:space="preserve">9467816</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
       <c r="H6">
-        <v>1658</v>
+        <v>1095</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -391,7 +391,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Odensevej 48</t>
+          <t xml:space="preserve">Grønlandsgade 1</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -401,16 +401,16 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t xml:space="preserve">727288, 9467816</t>
+          <t xml:space="preserve">727717, 5445867</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t xml:space="preserve">22</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H7">
-        <v>680</v>
+        <v>456</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -451,26 +451,26 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Søndre Havnekaj 10</t>
+          <t xml:space="preserve">Lindhøjvænget 1</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t xml:space="preserve">5300</t>
+          <t xml:space="preserve">5330</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t xml:space="preserve">727536, 7992424</t>
+          <t xml:space="preserve">2646560</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="H8">
-        <v>600</v>
+        <v>795</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -511,7 +511,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t xml:space="preserve">Marinavejen 12</t>
+          <t xml:space="preserve">Margrethes Plads 1</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -521,16 +521,16 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t xml:space="preserve">727707, 5445271</t>
+          <t xml:space="preserve">7885723, 100938670</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t xml:space="preserve">29</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="H9">
-        <v>1384</v>
+        <v>384</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -571,7 +571,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vejlevangen 18</t>
+          <t xml:space="preserve">Marinavejen 12</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -581,16 +581,16 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t xml:space="preserve">727715, 5446764</t>
+          <t xml:space="preserve">727707, 5445271</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">29</t>
         </is>
       </c>
       <c r="H10">
-        <v>356</v>
+        <v>1384</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -631,7 +631,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Grønlandsgade 1</t>
+          <t xml:space="preserve">Odensevej 48</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -641,16 +641,16 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t xml:space="preserve">727717, 5445867</t>
+          <t xml:space="preserve">727288, 9467816</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">22</t>
         </is>
       </c>
       <c r="H11">
-        <v>456</v>
+        <v>680</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -691,7 +691,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Margrethes Plads 1</t>
+          <t xml:space="preserve">Regnar Langesvej 1</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -701,16 +701,16 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t xml:space="preserve">7885723, 100938670</t>
+          <t xml:space="preserve">5447821</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">12</t>
         </is>
       </c>
       <c r="H12">
-        <v>384</v>
+        <v>345</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -751,7 +751,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t xml:space="preserve">Enggade 19</t>
+          <t xml:space="preserve">Søndre Havnekaj 10</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -761,16 +761,16 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t xml:space="preserve">9467816</t>
+          <t xml:space="preserve">727536, 7992424</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t xml:space="preserve">145</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H13">
-        <v>3083</v>
+        <v>600</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -811,7 +811,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Enggade 19</t>
+          <t xml:space="preserve">Vejlevangen 18</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -821,16 +821,16 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t xml:space="preserve">9467816</t>
+          <t xml:space="preserve">727715, 5446764</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H14">
-        <v>1095</v>
+        <v>356</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -1614,7 +1614,7 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t xml:space="preserve">311505577</t>
+          <t xml:space="preserve">311505585</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -1651,17 +1651,17 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lindøalleen 77</t>
+          <t xml:space="preserve">Fynshovedvej 486E</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t xml:space="preserve">5330</t>
+          <t xml:space="preserve">5390</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t xml:space="preserve">1329020</t>
+          <t xml:space="preserve">2649327</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -1670,11 +1670,11 @@
         </is>
       </c>
       <c r="H28">
-        <v>2329</v>
+        <v>919</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t xml:space="preserve">311505625</t>
+          <t xml:space="preserve">311505590</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -1711,17 +1711,17 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fynshovedvej 486E</t>
+          <t xml:space="preserve">Grønnegårds Alle 2</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t xml:space="preserve">5390</t>
+          <t xml:space="preserve">5300</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t xml:space="preserve">2649327</t>
+          <t xml:space="preserve">8045593</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -1730,11 +1730,11 @@
         </is>
       </c>
       <c r="H29">
-        <v>919</v>
+        <v>582</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t xml:space="preserve">311505590</t>
+          <t xml:space="preserve">311505594</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -1891,17 +1891,17 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t xml:space="preserve">Grønnegårds Alle 2</t>
+          <t xml:space="preserve">Lindøalleen 77</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t xml:space="preserve">5300</t>
+          <t xml:space="preserve">5330</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t xml:space="preserve">8045593</t>
+          <t xml:space="preserve">1329020</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -1910,11 +1910,11 @@
         </is>
       </c>
       <c r="H32">
-        <v>582</v>
+        <v>2329</v>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t xml:space="preserve">311505594</t>
+          <t xml:space="preserve">311505625</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -1951,7 +1951,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hans Tausensgade 29</t>
+          <t xml:space="preserve">Birkeparken 13</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -1961,20 +1961,20 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t xml:space="preserve">2642378</t>
+          <t xml:space="preserve">2658030</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="H33">
-        <v>344</v>
+        <v>260</v>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t xml:space="preserve">311518199</t>
+          <t xml:space="preserve">311518262</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -2011,7 +2011,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hans Tausensgade 29</t>
+          <t xml:space="preserve">Bispehaven 48</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -2021,20 +2021,20 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t xml:space="preserve">2642378</t>
+          <t xml:space="preserve">2642402</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H34">
-        <v>1019</v>
+        <v>260</v>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t xml:space="preserve">311518199</t>
+          <t xml:space="preserve">311598345</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -2071,17 +2071,17 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bispehaven 48</t>
+          <t xml:space="preserve">Borgmester Hansensvej 3</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t xml:space="preserve">5550</t>
+          <t xml:space="preserve">5300</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t xml:space="preserve">2642402</t>
+          <t xml:space="preserve">5446234</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -2090,11 +2090,11 @@
         </is>
       </c>
       <c r="H35">
-        <v>260</v>
+        <v>1516</v>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t xml:space="preserve">311598345</t>
+          <t xml:space="preserve">311518290</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t xml:space="preserve">Birkeparken 13</t>
+          <t xml:space="preserve">Hans Tausensgade 29</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -2141,20 +2141,20 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t xml:space="preserve">2658030</t>
+          <t xml:space="preserve">2642378</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H36">
-        <v>260</v>
+        <v>344</v>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t xml:space="preserve">311518262</t>
+          <t xml:space="preserve">311518199</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -2191,30 +2191,30 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kristine Rudesvej 23</t>
+          <t xml:space="preserve">Hans Tausensgade 29</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t xml:space="preserve">5300</t>
+          <t xml:space="preserve">5550</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t xml:space="preserve">5446101</t>
+          <t xml:space="preserve">2642378</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="H37">
-        <v>1797</v>
+        <v>1019</v>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t xml:space="preserve">311518286</t>
+          <t xml:space="preserve">311518199</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -2251,7 +2251,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t xml:space="preserve">Borgmester Hansensvej 3</t>
+          <t xml:space="preserve">Kohaven 8</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -2261,7 +2261,7 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t xml:space="preserve">5446234</t>
+          <t xml:space="preserve">5446917</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -2270,11 +2270,11 @@
         </is>
       </c>
       <c r="H38">
-        <v>1516</v>
+        <v>923</v>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t xml:space="preserve">311518290</t>
+          <t xml:space="preserve">311518236</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -2311,7 +2311,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kohaven 8</t>
+          <t xml:space="preserve">Kristine Rudesvej 23</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t xml:space="preserve">5446917</t>
+          <t xml:space="preserve">5446101</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
@@ -2330,11 +2330,11 @@
         </is>
       </c>
       <c r="H39">
-        <v>923</v>
+        <v>1797</v>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t xml:space="preserve">311518236</t>
+          <t xml:space="preserve">311518286</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -2371,17 +2371,17 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rosendalen 215</t>
+          <t xml:space="preserve">Lavindsgårdsvej 7</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t xml:space="preserve">5330</t>
+          <t xml:space="preserve">5550</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t xml:space="preserve">2646524</t>
+          <t xml:space="preserve">2657922</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -2390,11 +2390,11 @@
         </is>
       </c>
       <c r="H40">
-        <v>362</v>
+        <v>3580</v>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t xml:space="preserve">311526236</t>
+          <t xml:space="preserve">311526226</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -2431,17 +2431,17 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lavindsgårdsvej 7</t>
+          <t xml:space="preserve">Lindhøjvej 2</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t xml:space="preserve">5550</t>
+          <t xml:space="preserve">5330</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t xml:space="preserve">2657922</t>
+          <t xml:space="preserve">7771570</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
@@ -2450,11 +2450,11 @@
         </is>
       </c>
       <c r="H41">
-        <v>3580</v>
+        <v>4136</v>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t xml:space="preserve">311526227</t>
+          <t xml:space="preserve">311526259</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -2491,7 +2491,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lindhøjvej 2</t>
+          <t xml:space="preserve">Rosendalen 215</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -2501,7 +2501,7 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t xml:space="preserve">7771570</t>
+          <t xml:space="preserve">2646524</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
@@ -2510,11 +2510,11 @@
         </is>
       </c>
       <c r="H42">
-        <v>4136</v>
+        <v>362</v>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t xml:space="preserve">311526259</t>
+          <t xml:space="preserve">311526236</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -2551,7 +2551,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lindøalleen 51</t>
+          <t xml:space="preserve">Lindøalleen 47</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -2566,15 +2566,15 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="H43">
-        <v>7542</v>
+        <v>526</v>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t xml:space="preserve">311540126</t>
+          <t xml:space="preserve">311540125</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -2611,7 +2611,7 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lindøalleen 53</t>
+          <t xml:space="preserve">Lindøalleen 51</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -2626,15 +2626,15 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H44">
-        <v>1970</v>
+        <v>7542</v>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t xml:space="preserve">311540105</t>
+          <t xml:space="preserve">311540126</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
@@ -2671,7 +2671,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lindøalleen 47</t>
+          <t xml:space="preserve">Lindøalleen 53</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -2686,15 +2686,15 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H45">
-        <v>526</v>
+        <v>1970</v>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t xml:space="preserve">311540125</t>
+          <t xml:space="preserve">311540105</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
@@ -2814,7 +2814,7 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t xml:space="preserve">311557515</t>
+          <t xml:space="preserve">311557521</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
@@ -2874,7 +2874,7 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t xml:space="preserve">311557515</t>
+          <t xml:space="preserve">311557521</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
@@ -2934,7 +2934,7 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t xml:space="preserve">311557515</t>
+          <t xml:space="preserve">311557518</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
@@ -2994,7 +2994,7 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t xml:space="preserve">311557515</t>
+          <t xml:space="preserve">311557521</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
@@ -3271,30 +3271,30 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mesinge Bygade 51</t>
+          <t xml:space="preserve">Langegade 36</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t xml:space="preserve">5370</t>
+          <t xml:space="preserve">5300</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t xml:space="preserve">2644386</t>
+          <t xml:space="preserve">5445199</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H55">
-        <v>1673</v>
+        <v>426</v>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t xml:space="preserve">311590388</t>
+          <t xml:space="preserve">311590569</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
@@ -3331,30 +3331,30 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t xml:space="preserve">Langegade 36</t>
+          <t xml:space="preserve">Mesinge Bygade 51</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t xml:space="preserve">5300</t>
+          <t xml:space="preserve">5370</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t xml:space="preserve">5445199</t>
+          <t xml:space="preserve">2644386</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H56">
-        <v>426</v>
+        <v>1673</v>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t xml:space="preserve">311590569</t>
+          <t xml:space="preserve">311590388</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
@@ -3654,7 +3654,7 @@
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t xml:space="preserve">311597142</t>
+          <t xml:space="preserve">311597138</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
@@ -3751,7 +3751,7 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t xml:space="preserve">Strandgårds Alle 1</t>
+          <t xml:space="preserve">Nymarken 45</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -3761,20 +3761,20 @@
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t xml:space="preserve">100063809</t>
+          <t xml:space="preserve">2647942</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="H63">
-        <v>1109</v>
+        <v>603</v>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t xml:space="preserve">311598079</t>
+          <t xml:space="preserve">311598123</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
@@ -3811,7 +3811,7 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nymarken 45</t>
+          <t xml:space="preserve">Strandgårds Alle 1</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
@@ -3821,20 +3821,20 @@
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t xml:space="preserve">2647942</t>
+          <t xml:space="preserve">100063809</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H64">
-        <v>603</v>
+        <v>1109</v>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t xml:space="preserve">311598123</t>
+          <t xml:space="preserve">311598079</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
@@ -4171,7 +4171,7 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t xml:space="preserve">Marinavejen 8A</t>
+          <t xml:space="preserve">Marinavejen 4</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
@@ -4186,15 +4186,15 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t xml:space="preserve">51</t>
+          <t xml:space="preserve">53</t>
         </is>
       </c>
       <c r="H70">
-        <v>256</v>
+        <v>360</v>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t xml:space="preserve">311600397</t>
+          <t xml:space="preserve">311600401</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
@@ -4231,7 +4231,7 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t xml:space="preserve">Marinavejen 4</t>
+          <t xml:space="preserve">Marinavejen 8A</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
@@ -4246,15 +4246,15 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t xml:space="preserve">53</t>
+          <t xml:space="preserve">51</t>
         </is>
       </c>
       <c r="H71">
-        <v>360</v>
+        <v>256</v>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t xml:space="preserve">311600401</t>
+          <t xml:space="preserve">311600397</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
@@ -4411,7 +4411,7 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t xml:space="preserve">Møllevej 6A</t>
+          <t xml:space="preserve">Møllevej 61</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
@@ -4426,11 +4426,11 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H74">
-        <v>1869</v>
+        <v>738</v>
       </c>
       <c r="I74" t="inlineStr">
         <is>
@@ -4471,7 +4471,7 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t xml:space="preserve">Møllevej 61</t>
+          <t xml:space="preserve">Møllevej 6A</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
@@ -4486,11 +4486,11 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H75">
-        <v>738</v>
+        <v>1869</v>
       </c>
       <c r="I75" t="inlineStr">
         <is>
@@ -4831,7 +4831,7 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rønningevej 38</t>
+          <t xml:space="preserve">Børmosevej 3</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
@@ -4846,15 +4846,15 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="H81">
-        <v>7353</v>
+        <v>3458</v>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t xml:space="preserve">311617388</t>
+          <t xml:space="preserve">311617330</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
@@ -4891,7 +4891,7 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t xml:space="preserve">Børmosevej 3</t>
+          <t xml:space="preserve">Rønningevej 38</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
@@ -4906,15 +4906,15 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H82">
-        <v>3458</v>
+        <v>7353</v>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t xml:space="preserve">311617330</t>
+          <t xml:space="preserve">311617388</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">

--- a/public/exports/29189706.xlsx
+++ b/public/exports/29189706.xlsx
@@ -1614,7 +1614,7 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t xml:space="preserve">311505585</t>
+          <t xml:space="preserve">311505577</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -2394,7 +2394,7 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t xml:space="preserve">311526226</t>
+          <t xml:space="preserve">311526227</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -2814,7 +2814,7 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t xml:space="preserve">311557521</t>
+          <t xml:space="preserve">311557515</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
@@ -2874,7 +2874,7 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t xml:space="preserve">311557521</t>
+          <t xml:space="preserve">311557515</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
@@ -2934,7 +2934,7 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t xml:space="preserve">311557518</t>
+          <t xml:space="preserve">311557515</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
@@ -2994,7 +2994,7 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t xml:space="preserve">311557521</t>
+          <t xml:space="preserve">311557515</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">

--- a/public/exports/29189706.xlsx
+++ b/public/exports/29189706.xlsx
@@ -9,7 +9,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:L97"/>
+  <dimension ref="A1:M97"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
@@ -59,15 +59,20 @@
       </c>
       <c r="J1" t="inlineStr">
         <is>
+          <t xml:space="preserve">Energimærkningsfirma</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
           <t xml:space="preserve">Gyldig til</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t xml:space="preserve">Status</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t xml:space="preserve">Mangler gyldigt mærke</t>
         </is>
@@ -124,10 +129,15 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -184,10 +194,15 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -244,10 +259,15 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
+      <c r="M4" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -304,10 +324,15 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
+      <c r="M5" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -364,10 +389,15 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr">
+      <c r="M6" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -424,10 +454,15 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr">
+      <c r="M7" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -484,10 +519,15 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr">
+      <c r="M8" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -544,10 +584,15 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr">
+      <c r="M9" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -604,10 +649,15 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr">
+      <c r="M10" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -664,10 +714,15 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L11" t="inlineStr">
+      <c r="M11" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -724,10 +779,15 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L12" t="inlineStr">
+      <c r="M12" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -784,10 +844,15 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L13" t="inlineStr">
+      <c r="M13" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -844,10 +909,15 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L14" t="inlineStr">
+      <c r="M14" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -899,15 +969,20 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
+          <t xml:space="preserve">Botjek Odense v. Blomberg Ingeniørfirma A/S</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
           <t xml:space="preserve">2019-06-23</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr">
+      <c r="L15" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L15" t="inlineStr">
+      <c r="M15" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -959,15 +1034,20 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
+          <t xml:space="preserve">Botjek Odense v. Blomberg Ingeniørfirma A/S</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
           <t xml:space="preserve">2019-06-29</t>
         </is>
       </c>
-      <c r="K16" t="inlineStr">
+      <c r="L16" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L16" t="inlineStr">
+      <c r="M16" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1019,15 +1099,20 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
+          <t xml:space="preserve">Jysk Trykprøvning A/S</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
           <t xml:space="preserve">2023-04-17</t>
         </is>
       </c>
-      <c r="K17" t="inlineStr">
+      <c r="L17" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L17" t="inlineStr">
+      <c r="M17" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1079,15 +1164,20 @@
       </c>
       <c r="J18" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
           <t xml:space="preserve">2024-07-07</t>
         </is>
       </c>
-      <c r="K18" t="inlineStr">
+      <c r="L18" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L18" t="inlineStr">
+      <c r="M18" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1139,15 +1229,20 @@
       </c>
       <c r="J19" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-12-20</t>
         </is>
       </c>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1199,15 +1294,20 @@
       </c>
       <c r="J20" t="inlineStr">
         <is>
+          <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
           <t xml:space="preserve">2030-12-17</t>
         </is>
       </c>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1259,15 +1359,20 @@
       </c>
       <c r="J21" t="inlineStr">
         <is>
+          <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-02-12</t>
         </is>
       </c>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1319,15 +1424,20 @@
       </c>
       <c r="J22" t="inlineStr">
         <is>
+          <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-02-12</t>
         </is>
       </c>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1379,15 +1489,20 @@
       </c>
       <c r="J23" t="inlineStr">
         <is>
+          <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-02-12</t>
         </is>
       </c>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1439,15 +1554,20 @@
       </c>
       <c r="J24" t="inlineStr">
         <is>
+          <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-02-22</t>
         </is>
       </c>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1499,15 +1619,20 @@
       </c>
       <c r="J25" t="inlineStr">
         <is>
+          <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-02-22</t>
         </is>
       </c>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1559,15 +1684,20 @@
       </c>
       <c r="J26" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-02-24</t>
         </is>
       </c>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1614,20 +1744,25 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t xml:space="preserve">311505577</t>
+          <t xml:space="preserve">311505585</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
+          <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-03-22</t>
         </is>
       </c>
-      <c r="K27" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1679,15 +1814,20 @@
       </c>
       <c r="J28" t="inlineStr">
         <is>
+          <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-03-22</t>
         </is>
       </c>
-      <c r="K28" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1739,15 +1879,20 @@
       </c>
       <c r="J29" t="inlineStr">
         <is>
+          <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-03-22</t>
         </is>
       </c>
-      <c r="K29" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1799,15 +1944,20 @@
       </c>
       <c r="J30" t="inlineStr">
         <is>
+          <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-03-22</t>
         </is>
       </c>
-      <c r="K30" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1859,15 +2009,20 @@
       </c>
       <c r="J31" t="inlineStr">
         <is>
+          <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-03-22</t>
         </is>
       </c>
-      <c r="K31" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1919,15 +2074,20 @@
       </c>
       <c r="J32" t="inlineStr">
         <is>
+          <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-03-22</t>
         </is>
       </c>
-      <c r="K32" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1979,15 +2139,20 @@
       </c>
       <c r="J33" t="inlineStr">
         <is>
+          <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-05-06</t>
         </is>
       </c>
-      <c r="K33" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2039,15 +2204,20 @@
       </c>
       <c r="J34" t="inlineStr">
         <is>
+          <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-05-06</t>
         </is>
       </c>
-      <c r="K34" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2099,15 +2269,20 @@
       </c>
       <c r="J35" t="inlineStr">
         <is>
+          <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-05-06</t>
         </is>
       </c>
-      <c r="K35" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2159,15 +2334,20 @@
       </c>
       <c r="J36" t="inlineStr">
         <is>
+          <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-05-06</t>
         </is>
       </c>
-      <c r="K36" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2219,15 +2399,20 @@
       </c>
       <c r="J37" t="inlineStr">
         <is>
+          <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-05-06</t>
         </is>
       </c>
-      <c r="K37" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2279,15 +2464,20 @@
       </c>
       <c r="J38" t="inlineStr">
         <is>
+          <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-05-06</t>
         </is>
       </c>
-      <c r="K38" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2339,15 +2529,20 @@
       </c>
       <c r="J39" t="inlineStr">
         <is>
+          <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-05-06</t>
         </is>
       </c>
-      <c r="K39" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2394,20 +2589,25 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t xml:space="preserve">311526227</t>
+          <t xml:space="preserve">311526226</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
+          <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-06-08</t>
         </is>
       </c>
-      <c r="K40" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2459,15 +2659,20 @@
       </c>
       <c r="J41" t="inlineStr">
         <is>
+          <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-06-08</t>
         </is>
       </c>
-      <c r="K41" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2519,15 +2724,20 @@
       </c>
       <c r="J42" t="inlineStr">
         <is>
+          <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-06-08</t>
         </is>
       </c>
-      <c r="K42" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2579,15 +2789,20 @@
       </c>
       <c r="J43" t="inlineStr">
         <is>
+          <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-08-11</t>
         </is>
       </c>
-      <c r="K43" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2639,15 +2854,20 @@
       </c>
       <c r="J44" t="inlineStr">
         <is>
+          <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-08-11</t>
         </is>
       </c>
-      <c r="K44" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L44" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2699,15 +2919,20 @@
       </c>
       <c r="J45" t="inlineStr">
         <is>
+          <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-08-11</t>
         </is>
       </c>
-      <c r="K45" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2759,15 +2984,20 @@
       </c>
       <c r="J46" t="inlineStr">
         <is>
+          <t xml:space="preserve">BMH Rådgivning ApS</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-09-03</t>
         </is>
       </c>
-      <c r="K46" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2819,15 +3049,20 @@
       </c>
       <c r="J47" t="inlineStr">
         <is>
+          <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-10-26</t>
         </is>
       </c>
-      <c r="K47" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2879,15 +3114,20 @@
       </c>
       <c r="J48" t="inlineStr">
         <is>
+          <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-10-26</t>
         </is>
       </c>
-      <c r="K48" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2934,20 +3174,25 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t xml:space="preserve">311557515</t>
+          <t xml:space="preserve">311557518</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
+          <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-10-26</t>
         </is>
       </c>
-      <c r="K49" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2999,15 +3244,20 @@
       </c>
       <c r="J50" t="inlineStr">
         <is>
+          <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-10-26</t>
         </is>
       </c>
-      <c r="K50" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3059,15 +3309,20 @@
       </c>
       <c r="J51" t="inlineStr">
         <is>
+          <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-03-18</t>
         </is>
       </c>
-      <c r="K51" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3119,15 +3374,20 @@
       </c>
       <c r="J52" t="inlineStr">
         <is>
+          <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-03-24</t>
         </is>
       </c>
-      <c r="K52" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L52" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3179,15 +3439,20 @@
       </c>
       <c r="J53" t="inlineStr">
         <is>
+          <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-03-31</t>
         </is>
       </c>
-      <c r="K53" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L53" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3239,15 +3504,20 @@
       </c>
       <c r="J54" t="inlineStr">
         <is>
+          <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-03-31</t>
         </is>
       </c>
-      <c r="K54" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L54" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3299,15 +3569,20 @@
       </c>
       <c r="J55" t="inlineStr">
         <is>
+          <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-04-04</t>
         </is>
       </c>
-      <c r="K55" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3359,15 +3634,20 @@
       </c>
       <c r="J56" t="inlineStr">
         <is>
+          <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-04-04</t>
         </is>
       </c>
-      <c r="K56" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M56" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3419,15 +3699,20 @@
       </c>
       <c r="J57" t="inlineStr">
         <is>
+          <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-04-10</t>
         </is>
       </c>
-      <c r="K57" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M57" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3479,15 +3764,20 @@
       </c>
       <c r="J58" t="inlineStr">
         <is>
+          <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-04-22</t>
         </is>
       </c>
-      <c r="K58" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L58" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M58" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3539,15 +3829,20 @@
       </c>
       <c r="J59" t="inlineStr">
         <is>
+          <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-04-25</t>
         </is>
       </c>
-      <c r="K59" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L59" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M59" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3599,15 +3894,20 @@
       </c>
       <c r="J60" t="inlineStr">
         <is>
+          <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-04-28</t>
         </is>
       </c>
-      <c r="K60" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L60" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M60" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3659,15 +3959,20 @@
       </c>
       <c r="J61" t="inlineStr">
         <is>
+          <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-05-02</t>
         </is>
       </c>
-      <c r="K61" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L61" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M61" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3719,15 +4024,20 @@
       </c>
       <c r="J62" t="inlineStr">
         <is>
+          <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-05-03</t>
         </is>
       </c>
-      <c r="K62" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L62" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M62" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3779,15 +4089,20 @@
       </c>
       <c r="J63" t="inlineStr">
         <is>
+          <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-05-05</t>
         </is>
       </c>
-      <c r="K63" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L63" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M63" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3839,15 +4154,20 @@
       </c>
       <c r="J64" t="inlineStr">
         <is>
+          <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-05-05</t>
         </is>
       </c>
-      <c r="K64" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L64" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M64" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3899,15 +4219,20 @@
       </c>
       <c r="J65" t="inlineStr">
         <is>
+          <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-05-09</t>
         </is>
       </c>
-      <c r="K65" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L65" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M65" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3959,15 +4284,20 @@
       </c>
       <c r="J66" t="inlineStr">
         <is>
+          <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-05-10</t>
         </is>
       </c>
-      <c r="K66" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L66" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M66" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4019,15 +4349,20 @@
       </c>
       <c r="J67" t="inlineStr">
         <is>
+          <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-05-10</t>
         </is>
       </c>
-      <c r="K67" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L67" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M67" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4079,15 +4414,20 @@
       </c>
       <c r="J68" t="inlineStr">
         <is>
+          <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-05-10</t>
         </is>
       </c>
-      <c r="K68" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L68" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M68" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4139,15 +4479,20 @@
       </c>
       <c r="J69" t="inlineStr">
         <is>
+          <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-05-10</t>
         </is>
       </c>
-      <c r="K69" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L69" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M69" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4199,15 +4544,20 @@
       </c>
       <c r="J70" t="inlineStr">
         <is>
+          <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-05-16</t>
         </is>
       </c>
-      <c r="K70" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L70" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M70" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4259,15 +4609,20 @@
       </c>
       <c r="J71" t="inlineStr">
         <is>
+          <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-05-16</t>
         </is>
       </c>
-      <c r="K71" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L71" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M71" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4319,15 +4674,20 @@
       </c>
       <c r="J72" t="inlineStr">
         <is>
+          <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-05-18</t>
         </is>
       </c>
-      <c r="K72" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L72" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M72" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4379,15 +4739,20 @@
       </c>
       <c r="J73" t="inlineStr">
         <is>
+          <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-05-18</t>
         </is>
       </c>
-      <c r="K73" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L73" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M73" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4439,15 +4804,20 @@
       </c>
       <c r="J74" t="inlineStr">
         <is>
+          <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-05-18</t>
         </is>
       </c>
-      <c r="K74" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L74" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M74" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4499,15 +4869,20 @@
       </c>
       <c r="J75" t="inlineStr">
         <is>
+          <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-05-18</t>
         </is>
       </c>
-      <c r="K75" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L75" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M75" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4559,15 +4934,20 @@
       </c>
       <c r="J76" t="inlineStr">
         <is>
+          <t xml:space="preserve">Andel Energi A/S</t>
+        </is>
+      </c>
+      <c r="K76" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-05-24</t>
         </is>
       </c>
-      <c r="K76" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L76" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M76" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4619,15 +4999,20 @@
       </c>
       <c r="J77" t="inlineStr">
         <is>
+          <t xml:space="preserve">Andel Energi A/S</t>
+        </is>
+      </c>
+      <c r="K77" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-05-31</t>
         </is>
       </c>
-      <c r="K77" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L77" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M77" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4679,15 +5064,20 @@
       </c>
       <c r="J78" t="inlineStr">
         <is>
+          <t xml:space="preserve">Andel Energi A/S</t>
+        </is>
+      </c>
+      <c r="K78" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-07-18</t>
         </is>
       </c>
-      <c r="K78" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L78" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M78" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4739,15 +5129,20 @@
       </c>
       <c r="J79" t="inlineStr">
         <is>
+          <t xml:space="preserve">Andel Energi A/S</t>
+        </is>
+      </c>
+      <c r="K79" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-07-18</t>
         </is>
       </c>
-      <c r="K79" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L79" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M79" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4799,15 +5194,20 @@
       </c>
       <c r="J80" t="inlineStr">
         <is>
+          <t xml:space="preserve">Andel Energi A/S</t>
+        </is>
+      </c>
+      <c r="K80" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-07-18</t>
         </is>
       </c>
-      <c r="K80" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L80" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M80" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4859,15 +5259,20 @@
       </c>
       <c r="J81" t="inlineStr">
         <is>
+          <t xml:space="preserve">Andel Energi A/S</t>
+        </is>
+      </c>
+      <c r="K81" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-07-27</t>
         </is>
       </c>
-      <c r="K81" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M81" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4919,15 +5324,20 @@
       </c>
       <c r="J82" t="inlineStr">
         <is>
+          <t xml:space="preserve">Andel Energi A/S</t>
+        </is>
+      </c>
+      <c r="K82" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-07-27</t>
         </is>
       </c>
-      <c r="K82" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L82" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M82" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4979,15 +5389,20 @@
       </c>
       <c r="J83" t="inlineStr">
         <is>
+          <t xml:space="preserve">Promana A/S</t>
+        </is>
+      </c>
+      <c r="K83" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-08-19</t>
         </is>
       </c>
-      <c r="K83" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L83" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M83" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5039,15 +5454,20 @@
       </c>
       <c r="J84" t="inlineStr">
         <is>
+          <t xml:space="preserve">Vh-consult</t>
+        </is>
+      </c>
+      <c r="K84" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-04-25</t>
         </is>
       </c>
-      <c r="K84" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L84" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M84" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5099,15 +5519,20 @@
       </c>
       <c r="J85" t="inlineStr">
         <is>
+          <t xml:space="preserve">Vh-consult</t>
+        </is>
+      </c>
+      <c r="K85" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-04-25</t>
         </is>
       </c>
-      <c r="K85" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L85" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M85" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5159,15 +5584,20 @@
       </c>
       <c r="J86" t="inlineStr">
         <is>
+          <t xml:space="preserve">Vh-consult</t>
+        </is>
+      </c>
+      <c r="K86" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-04-25</t>
         </is>
       </c>
-      <c r="K86" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L86" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M86" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5219,15 +5649,20 @@
       </c>
       <c r="J87" t="inlineStr">
         <is>
+          <t xml:space="preserve">Vh-consult</t>
+        </is>
+      </c>
+      <c r="K87" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-04-25</t>
         </is>
       </c>
-      <c r="K87" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L87" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M87" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5279,15 +5714,20 @@
       </c>
       <c r="J88" t="inlineStr">
         <is>
+          <t xml:space="preserve">Vh-consult</t>
+        </is>
+      </c>
+      <c r="K88" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-04-25</t>
         </is>
       </c>
-      <c r="K88" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L88" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M88" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5339,15 +5779,20 @@
       </c>
       <c r="J89" t="inlineStr">
         <is>
+          <t xml:space="preserve">Inspec ApS</t>
+        </is>
+      </c>
+      <c r="K89" t="inlineStr">
+        <is>
           <t xml:space="preserve">2034-02-08</t>
         </is>
       </c>
-      <c r="K89" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L89" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M89" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5399,15 +5844,20 @@
       </c>
       <c r="J90" t="inlineStr">
         <is>
+          <t xml:space="preserve">CB Group ApS</t>
+        </is>
+      </c>
+      <c r="K90" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-08-29</t>
         </is>
       </c>
-      <c r="K90" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L90" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M90" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5459,15 +5909,20 @@
       </c>
       <c r="J91" t="inlineStr">
         <is>
+          <t xml:space="preserve">NRGi Rådgivning A/S</t>
+        </is>
+      </c>
+      <c r="K91" t="inlineStr">
+        <is>
           <t xml:space="preserve">2036-02-17</t>
         </is>
       </c>
-      <c r="K91" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L91" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M91" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5519,15 +5974,20 @@
       </c>
       <c r="J92" t="inlineStr">
         <is>
+          <t xml:space="preserve">NRGi Rådgivning A/S</t>
+        </is>
+      </c>
+      <c r="K92" t="inlineStr">
+        <is>
           <t xml:space="preserve">2036-02-25</t>
         </is>
       </c>
-      <c r="K92" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L92" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M92" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5579,15 +6039,20 @@
       </c>
       <c r="J93" t="inlineStr">
         <is>
+          <t xml:space="preserve">NRGi Rådgivning A/S</t>
+        </is>
+      </c>
+      <c r="K93" t="inlineStr">
+        <is>
           <t xml:space="preserve">2036-02-25</t>
         </is>
       </c>
-      <c r="K93" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L93" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M93" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5639,15 +6104,20 @@
       </c>
       <c r="J94" t="inlineStr">
         <is>
+          <t xml:space="preserve">NRGi Rådgivning A/S</t>
+        </is>
+      </c>
+      <c r="K94" t="inlineStr">
+        <is>
           <t xml:space="preserve">2036-02-25</t>
         </is>
       </c>
-      <c r="K94" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L94" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M94" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5699,15 +6169,20 @@
       </c>
       <c r="J95" t="inlineStr">
         <is>
+          <t xml:space="preserve">NRGi Rådgivning A/S</t>
+        </is>
+      </c>
+      <c r="K95" t="inlineStr">
+        <is>
           <t xml:space="preserve">2036-02-25</t>
         </is>
       </c>
-      <c r="K95" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L95" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M95" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5759,15 +6234,20 @@
       </c>
       <c r="J96" t="inlineStr">
         <is>
+          <t xml:space="preserve">NRGi Rådgivning A/S</t>
+        </is>
+      </c>
+      <c r="K96" t="inlineStr">
+        <is>
           <t xml:space="preserve">2036-02-25</t>
         </is>
       </c>
-      <c r="K96" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L96" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M96" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5819,21 +6299,26 @@
       </c>
       <c r="J97" t="inlineStr">
         <is>
+          <t xml:space="preserve">CB Group ApS</t>
+        </is>
+      </c>
+      <c r="K97" t="inlineStr">
+        <is>
           <t xml:space="preserve">2036-06-30</t>
         </is>
       </c>
-      <c r="K97" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L97" t="inlineStr">
         <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M97" t="inlineStr">
+        <is>
           <t xml:space="preserve">Nej</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:L97"/>
+  <autoFilter ref="A1:M97"/>
 </worksheet>
 </file>
--- a/public/exports/29189706.xlsx
+++ b/public/exports/29189706.xlsx
@@ -1744,12 +1744,12 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t xml:space="preserve">311505585</t>
+          <t xml:space="preserve">311505577</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="K27" t="inlineStr">
@@ -3174,7 +3174,7 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t xml:space="preserve">311557518</t>
+          <t xml:space="preserve">311557515</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
